--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-24T19:48:18+00:00</t>
+    <t>2024-10-29T08:42:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6584" uniqueCount="795">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6584" uniqueCount="797">
   <si>
     <t>Property</t>
   </si>
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T08:42:45+00:00</t>
+    <t>2024-10-29T10:21:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -455,10 +455,10 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Claim.extension:Note</t>
-  </si>
-  <si>
-    <t>Note</t>
+    <t>Claim.extension:notiz</t>
+  </si>
+  <si>
+    <t>notiz</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {note}
@@ -474,26 +474,26 @@
     <t>This extension SHALL NOT be used if the resource already has standard 'note' element (or equivalent) of type Annotation on the same element</t>
   </si>
   <si>
-    <t>Claim.extension:DiagnosisRelatedNode</t>
-  </si>
-  <si>
-    <t>DiagnosisRelatedNode</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-diagnosisRelatedNode}
+    <t>Claim.extension:diagnoseKnoten</t>
+  </si>
+  <si>
+    <t>diagnoseKnoten</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-diagnoseKnoten}
 </t>
   </si>
   <si>
     <t>"Abrechnung - Knoten:" Lukriert die Patient:innen über eine reguläre Gruppe Punkte, so ist in diesem Datenfeld die entsprechende Knotenbezeichnung einzutragen.</t>
   </si>
   <si>
-    <t>Claim.extension:LKFPunkte</t>
-  </si>
-  <si>
-    <t>LKFPunkte</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/lkfPunkte}
+    <t>Claim.extension:lkfPunkte</t>
+  </si>
+  <si>
+    <t>lkfPunkte</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-lkfPunkte}
 </t>
   </si>
   <si>
@@ -503,13 +503,13 @@
     <t>In dieser Extension werden alle möglichen Punkteangaben im LKF zusammengefasst.</t>
   </si>
   <si>
-    <t>Claim.extension:ErrorWarning</t>
-  </si>
-  <si>
-    <t>ErrorWarning</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-ErrorWarning}
+    <t>Claim.extension:fehlerWarnung</t>
+  </si>
+  <si>
+    <t>fehlerWarnung</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-fehlerWarnung}
 </t>
   </si>
   <si>
@@ -519,39 +519,45 @@
     <t>MOPED Extension für akzeptierte Errors und Warnings</t>
   </si>
   <si>
-    <t>Claim.extension:Fondsrelevanz</t>
-  </si>
-  <si>
-    <t>Fondsrelevanz</t>
+    <t>Claim.extension:fondRelevant</t>
+  </si>
+  <si>
+    <t>fondRelevant</t>
   </si>
   <si>
     <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-fondsrelevanz}
 </t>
   </si>
   <si>
+    <t>Fondsrelevanz</t>
+  </si>
+  <si>
     <t>Hier ist anzugeben, ob der stationäre Aufenthalt/ambulante Besuch gegenüber dem Landesgesundheitsfonds/PRIKRAF abzurechnen ist.</t>
   </si>
   <si>
-    <t>Claim.extension:Plausibilitaetskennzeichen</t>
+    <t>Claim.extension:plausibilitaetskennzeichen</t>
+  </si>
+  <si>
+    <t>plausibilitaetskennzeichen</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-plausibilitaetskennzeichen}
+</t>
   </si>
   <si>
     <t>Plausibilitaetskennzeichen</t>
   </si>
   <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/Plausibilitaetskennzeichen}
-</t>
-  </si>
-  <si>
     <t>Dieses Datenfeld enthält eine Kennzeichnung als Ergebnis der vom Gesundheitsministerium vorgegebenen Plausibilitätsprüfung.</t>
   </si>
   <si>
-    <t>Claim.extension:SVAbrechnungsquartal</t>
-  </si>
-  <si>
-    <t>SVAbrechnungsquartal</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/SVAbrechnungsquartal}
+    <t>Claim.extension:svAbrechnungsquartal</t>
+  </si>
+  <si>
+    <t>svAbrechnungsquartal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-svAbrechnungsquartal}
 </t>
   </si>
   <si>
@@ -1625,13 +1631,13 @@
     <t>Claim.procedure.extension</t>
   </si>
   <si>
-    <t>Claim.procedure.extension:AbrechnungsRelevanz</t>
-  </si>
-  <si>
-    <t>AbrechnungsRelevanz</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-AbrechnungsRelevanz}
+    <t>Claim.procedure.extension:abrechnungsRelevanz</t>
+  </si>
+  <si>
+    <t>abrechnungsRelevanz</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://example.org/StructureDefinition/moped-ext-abrechnungsRelevanz}
 </t>
   </si>
   <si>
@@ -2774,9 +2780,9 @@
   <dimension ref="A1:AM186"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.83203125" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.703125" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="46.109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="25.31640625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="25.375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="48.5859375" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -4294,10 +4300,10 @@
         <v>163</v>
       </c>
       <c r="L14" t="s" s="2">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="M14" t="s" s="2">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="N14" s="2"/>
       <c r="O14" s="2"/>
@@ -4374,13 +4380,13 @@
     </row>
     <row r="15">
       <c r="A15" t="s" s="2">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B15" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C15" t="s" s="2">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="D15" t="s" s="2">
         <v>19</v>
@@ -4402,13 +4408,13 @@
         <v>19</v>
       </c>
       <c r="K15" t="s" s="2">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="L15" t="s" s="2">
-        <v>166</v>
+        <v>169</v>
       </c>
       <c r="M15" t="s" s="2">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="N15" s="2"/>
       <c r="O15" s="2"/>
@@ -4485,13 +4491,13 @@
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="B16" t="s" s="2">
         <v>133</v>
       </c>
       <c r="C16" t="s" s="2">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="D16" t="s" s="2">
         <v>19</v>
@@ -4513,13 +4519,13 @@
         <v>19</v>
       </c>
       <c r="K16" t="s" s="2">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="L16" t="s" s="2">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="M16" t="s" s="2">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="N16" s="2"/>
       <c r="O16" s="2"/>
@@ -4596,14 +4602,14 @@
     </row>
     <row r="17">
       <c r="A17" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B17" t="s" s="2">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C17" s="2"/>
       <c r="D17" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E17" s="2"/>
       <c r="F17" t="s" s="2">
@@ -4625,16 +4631,16 @@
         <v>134</v>
       </c>
       <c r="L17" t="s" s="2">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="M17" t="s" s="2">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="N17" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O17" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P17" t="s" s="2">
         <v>19</v>
@@ -4683,7 +4689,7 @@
         <v>19</v>
       </c>
       <c r="AF17" t="s" s="2">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="AG17" t="s" s="2">
         <v>76</v>
@@ -4709,14 +4715,14 @@
     </row>
     <row r="18">
       <c r="A18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="B18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C18" s="2"/>
       <c r="D18" t="s" s="2">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="E18" s="2"/>
       <c r="F18" t="s" s="2">
@@ -4735,17 +4741,17 @@
         <v>19</v>
       </c>
       <c r="K18" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L18" t="s" s="2">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="M18" t="s" s="2">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="N18" s="2"/>
       <c r="O18" t="s" s="2">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="P18" t="s" s="2">
         <v>19</v>
@@ -4794,7 +4800,7 @@
         <v>19</v>
       </c>
       <c r="AF18" t="s" s="2">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="AG18" t="s" s="2">
         <v>76</v>
@@ -4809,10 +4815,10 @@
         <v>99</v>
       </c>
       <c r="AK18" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL18" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM18" t="s" s="2">
         <v>19</v>
@@ -4820,10 +4826,10 @@
     </row>
     <row r="19">
       <c r="A19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="B19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C19" s="2"/>
       <c r="D19" t="s" s="2">
@@ -4846,17 +4852,17 @@
         <v>19</v>
       </c>
       <c r="K19" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L19" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M19" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N19" s="2"/>
       <c r="O19" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P19" t="s" s="2">
         <v>19</v>
@@ -4905,7 +4911,7 @@
         <v>19</v>
       </c>
       <c r="AF19" t="s" s="2">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="AG19" t="s" s="2">
         <v>76</v>
@@ -4931,10 +4937,10 @@
     </row>
     <row r="20">
       <c r="A20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="B20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C20" s="2"/>
       <c r="D20" t="s" s="2">
@@ -4960,16 +4966,16 @@
         <v>107</v>
       </c>
       <c r="L20" t="s" s="2">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="M20" t="s" s="2">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="N20" t="s" s="2">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O20" t="s" s="2">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="P20" t="s" s="2">
         <v>19</v>
@@ -4997,10 +5003,10 @@
         <v>111</v>
       </c>
       <c r="Y20" t="s" s="2">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="Z20" t="s" s="2">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="AA20" t="s" s="2">
         <v>19</v>
@@ -5018,7 +5024,7 @@
         <v>19</v>
       </c>
       <c r="AF20" t="s" s="2">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="AG20" t="s" s="2">
         <v>87</v>
@@ -5033,10 +5039,10 @@
         <v>99</v>
       </c>
       <c r="AK20" t="s" s="2">
-        <v>200</v>
+        <v>202</v>
       </c>
       <c r="AL20" t="s" s="2">
-        <v>201</v>
+        <v>203</v>
       </c>
       <c r="AM20" t="s" s="2">
         <v>19</v>
@@ -5044,10 +5050,10 @@
     </row>
     <row r="21">
       <c r="A21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="B21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="C21" s="2"/>
       <c r="D21" t="s" s="2">
@@ -5070,19 +5076,19 @@
         <v>88</v>
       </c>
       <c r="K21" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L21" t="s" s="2">
-        <v>204</v>
+        <v>206</v>
       </c>
       <c r="M21" t="s" s="2">
-        <v>205</v>
+        <v>207</v>
       </c>
       <c r="N21" t="s" s="2">
-        <v>206</v>
+        <v>208</v>
       </c>
       <c r="O21" t="s" s="2">
-        <v>207</v>
+        <v>209</v>
       </c>
       <c r="P21" t="s" s="2">
         <v>19</v>
@@ -5107,13 +5113,13 @@
         <v>19</v>
       </c>
       <c r="X21" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y21" t="s" s="2">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="Z21" t="s" s="2">
-        <v>210</v>
+        <v>212</v>
       </c>
       <c r="AA21" t="s" s="2">
         <v>19</v>
@@ -5131,7 +5137,7 @@
         <v>19</v>
       </c>
       <c r="AF21" t="s" s="2">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="AG21" t="s" s="2">
         <v>87</v>
@@ -5149,7 +5155,7 @@
         <v>19</v>
       </c>
       <c r="AL21" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM21" t="s" s="2">
         <v>19</v>
@@ -5157,10 +5163,10 @@
     </row>
     <row r="22">
       <c r="A22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="B22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="C22" s="2"/>
       <c r="D22" t="s" s="2">
@@ -5183,19 +5189,19 @@
         <v>19</v>
       </c>
       <c r="K22" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L22" t="s" s="2">
-        <v>213</v>
+        <v>215</v>
       </c>
       <c r="M22" t="s" s="2">
-        <v>214</v>
+        <v>216</v>
       </c>
       <c r="N22" t="s" s="2">
-        <v>215</v>
+        <v>217</v>
       </c>
       <c r="O22" t="s" s="2">
-        <v>216</v>
+        <v>218</v>
       </c>
       <c r="P22" t="s" s="2">
         <v>19</v>
@@ -5220,13 +5226,13 @@
         <v>19</v>
       </c>
       <c r="X22" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y22" t="s" s="2">
-        <v>218</v>
+        <v>220</v>
       </c>
       <c r="Z22" t="s" s="2">
-        <v>219</v>
+        <v>221</v>
       </c>
       <c r="AA22" t="s" s="2">
         <v>19</v>
@@ -5244,7 +5250,7 @@
         <v>19</v>
       </c>
       <c r="AF22" t="s" s="2">
-        <v>212</v>
+        <v>214</v>
       </c>
       <c r="AG22" t="s" s="2">
         <v>76</v>
@@ -5262,7 +5268,7 @@
         <v>19</v>
       </c>
       <c r="AL22" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM22" t="s" s="2">
         <v>19</v>
@@ -5270,10 +5276,10 @@
     </row>
     <row r="23">
       <c r="A23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="B23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="C23" s="2"/>
       <c r="D23" t="s" s="2">
@@ -5299,14 +5305,14 @@
         <v>107</v>
       </c>
       <c r="L23" t="s" s="2">
-        <v>221</v>
+        <v>223</v>
       </c>
       <c r="M23" t="s" s="2">
-        <v>222</v>
+        <v>224</v>
       </c>
       <c r="N23" s="2"/>
       <c r="O23" t="s" s="2">
-        <v>223</v>
+        <v>225</v>
       </c>
       <c r="P23" t="s" s="2">
         <v>19</v>
@@ -5334,10 +5340,10 @@
         <v>111</v>
       </c>
       <c r="Y23" t="s" s="2">
-        <v>224</v>
+        <v>226</v>
       </c>
       <c r="Z23" t="s" s="2">
-        <v>225</v>
+        <v>227</v>
       </c>
       <c r="AA23" t="s" s="2">
         <v>19</v>
@@ -5355,7 +5361,7 @@
         <v>19</v>
       </c>
       <c r="AF23" t="s" s="2">
-        <v>220</v>
+        <v>222</v>
       </c>
       <c r="AG23" t="s" s="2">
         <v>87</v>
@@ -5373,7 +5379,7 @@
         <v>19</v>
       </c>
       <c r="AL23" t="s" s="2">
-        <v>211</v>
+        <v>213</v>
       </c>
       <c r="AM23" t="s" s="2">
         <v>19</v>
@@ -5381,10 +5387,10 @@
     </row>
     <row r="24">
       <c r="A24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="B24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s" s="2">
@@ -5407,17 +5413,17 @@
         <v>88</v>
       </c>
       <c r="K24" t="s" s="2">
-        <v>227</v>
+        <v>229</v>
       </c>
       <c r="L24" t="s" s="2">
-        <v>228</v>
+        <v>230</v>
       </c>
       <c r="M24" t="s" s="2">
-        <v>229</v>
+        <v>231</v>
       </c>
       <c r="N24" s="2"/>
       <c r="O24" t="s" s="2">
-        <v>230</v>
+        <v>232</v>
       </c>
       <c r="P24" t="s" s="2">
         <v>19</v>
@@ -5466,7 +5472,7 @@
         <v>19</v>
       </c>
       <c r="AF24" t="s" s="2">
-        <v>226</v>
+        <v>228</v>
       </c>
       <c r="AG24" t="s" s="2">
         <v>87</v>
@@ -5481,10 +5487,10 @@
         <v>99</v>
       </c>
       <c r="AK24" t="s" s="2">
-        <v>231</v>
+        <v>233</v>
       </c>
       <c r="AL24" t="s" s="2">
-        <v>232</v>
+        <v>234</v>
       </c>
       <c r="AM24" t="s" s="2">
         <v>19</v>
@@ -5492,10 +5498,10 @@
     </row>
     <row r="25">
       <c r="A25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="B25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="C25" s="2"/>
       <c r="D25" t="s" s="2">
@@ -5518,19 +5524,19 @@
         <v>88</v>
       </c>
       <c r="K25" t="s" s="2">
-        <v>234</v>
+        <v>236</v>
       </c>
       <c r="L25" t="s" s="2">
-        <v>235</v>
+        <v>237</v>
       </c>
       <c r="M25" t="s" s="2">
-        <v>236</v>
+        <v>238</v>
       </c>
       <c r="N25" t="s" s="2">
-        <v>237</v>
+        <v>239</v>
       </c>
       <c r="O25" t="s" s="2">
-        <v>238</v>
+        <v>240</v>
       </c>
       <c r="P25" t="s" s="2">
         <v>19</v>
@@ -5579,7 +5585,7 @@
         <v>19</v>
       </c>
       <c r="AF25" t="s" s="2">
-        <v>233</v>
+        <v>235</v>
       </c>
       <c r="AG25" t="s" s="2">
         <v>76</v>
@@ -5597,7 +5603,7 @@
         <v>19</v>
       </c>
       <c r="AL25" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM25" t="s" s="2">
         <v>19</v>
@@ -5605,10 +5611,10 @@
     </row>
     <row r="26">
       <c r="A26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="B26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="C26" s="2"/>
       <c r="D26" t="s" s="2">
@@ -5631,19 +5637,19 @@
         <v>88</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>242</v>
+        <v>244</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>243</v>
+        <v>245</v>
       </c>
       <c r="N26" t="s" s="2">
-        <v>244</v>
+        <v>246</v>
       </c>
       <c r="O26" t="s" s="2">
-        <v>245</v>
+        <v>247</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -5692,7 +5698,7 @@
         <v>19</v>
       </c>
       <c r="AF26" t="s" s="2">
-        <v>240</v>
+        <v>242</v>
       </c>
       <c r="AG26" t="s" s="2">
         <v>87</v>
@@ -5707,10 +5713,10 @@
         <v>99</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>246</v>
+        <v>248</v>
       </c>
       <c r="AL26" t="s" s="2">
-        <v>247</v>
+        <v>249</v>
       </c>
       <c r="AM26" t="s" s="2">
         <v>19</v>
@@ -5718,10 +5724,10 @@
     </row>
     <row r="27">
       <c r="A27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5744,17 +5750,17 @@
         <v>19</v>
       </c>
       <c r="K27" t="s" s="2">
-        <v>249</v>
+        <v>251</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>250</v>
+        <v>252</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>251</v>
+        <v>253</v>
       </c>
       <c r="N27" s="2"/>
       <c r="O27" t="s" s="2">
-        <v>252</v>
+        <v>254</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -5803,7 +5809,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>248</v>
+        <v>250</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>76</v>
@@ -5821,7 +5827,7 @@
         <v>19</v>
       </c>
       <c r="AL27" t="s" s="2">
-        <v>253</v>
+        <v>255</v>
       </c>
       <c r="AM27" t="s" s="2">
         <v>19</v>
@@ -5829,10 +5835,10 @@
     </row>
     <row r="28">
       <c r="A28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5855,13 +5861,13 @@
         <v>88</v>
       </c>
       <c r="K28" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>256</v>
+        <v>258</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>257</v>
+        <v>259</v>
       </c>
       <c r="N28" s="2"/>
       <c r="O28" s="2"/>
@@ -5912,7 +5918,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>254</v>
+        <v>256</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>76</v>
@@ -5927,7 +5933,7 @@
         <v>99</v>
       </c>
       <c r="AK28" t="s" s="2">
-        <v>258</v>
+        <v>260</v>
       </c>
       <c r="AL28" t="s" s="2">
         <v>19</v>
@@ -5938,10 +5944,10 @@
     </row>
     <row r="29">
       <c r="A29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5964,16 +5970,16 @@
         <v>88</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>255</v>
+        <v>257</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>260</v>
+        <v>262</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>261</v>
+        <v>263</v>
       </c>
       <c r="N29" t="s" s="2">
-        <v>262</v>
+        <v>264</v>
       </c>
       <c r="O29" s="2"/>
       <c r="P29" t="s" s="2">
@@ -6023,7 +6029,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>259</v>
+        <v>261</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>76</v>
@@ -6038,10 +6044,10 @@
         <v>99</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>263</v>
+        <v>265</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>264</v>
+        <v>266</v>
       </c>
       <c r="AM29" t="s" s="2">
         <v>19</v>
@@ -6049,10 +6055,10 @@
     </row>
     <row r="30">
       <c r="A30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -6075,19 +6081,19 @@
         <v>88</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>266</v>
+        <v>268</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>267</v>
+        <v>269</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>268</v>
+        <v>270</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>269</v>
+        <v>271</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -6112,13 +6118,13 @@
         <v>19</v>
       </c>
       <c r="X30" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y30" t="s" s="2">
-        <v>270</v>
+        <v>272</v>
       </c>
       <c r="Z30" t="s" s="2">
-        <v>271</v>
+        <v>273</v>
       </c>
       <c r="AA30" t="s" s="2">
         <v>19</v>
@@ -6136,7 +6142,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>265</v>
+        <v>267</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>76</v>
@@ -6151,7 +6157,7 @@
         <v>99</v>
       </c>
       <c r="AK30" t="s" s="2">
-        <v>272</v>
+        <v>274</v>
       </c>
       <c r="AL30" t="s" s="2">
         <v>19</v>
@@ -6162,14 +6168,14 @@
     </row>
     <row r="31">
       <c r="A31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
-        <v>274</v>
+        <v>276</v>
       </c>
       <c r="E31" s="2"/>
       <c r="F31" t="s" s="2">
@@ -6188,19 +6194,19 @@
         <v>19</v>
       </c>
       <c r="K31" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>275</v>
+        <v>277</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>276</v>
+        <v>278</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>277</v>
+        <v>279</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>278</v>
+        <v>280</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -6225,13 +6231,13 @@
         <v>19</v>
       </c>
       <c r="X31" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y31" t="s" s="2">
-        <v>279</v>
+        <v>281</v>
       </c>
       <c r="Z31" t="s" s="2">
-        <v>280</v>
+        <v>282</v>
       </c>
       <c r="AA31" t="s" s="2">
         <v>19</v>
@@ -6249,7 +6255,7 @@
         <v>19</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>273</v>
+        <v>275</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>76</v>
@@ -6275,10 +6281,10 @@
     </row>
     <row r="32">
       <c r="A32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -6301,19 +6307,19 @@
         <v>19</v>
       </c>
       <c r="K32" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L32" t="s" s="2">
-        <v>283</v>
+        <v>285</v>
       </c>
       <c r="M32" t="s" s="2">
-        <v>284</v>
+        <v>286</v>
       </c>
       <c r="N32" t="s" s="2">
-        <v>285</v>
+        <v>287</v>
       </c>
       <c r="O32" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P32" t="s" s="2">
         <v>19</v>
@@ -6362,7 +6368,7 @@
         <v>19</v>
       </c>
       <c r="AF32" t="s" s="2">
-        <v>281</v>
+        <v>283</v>
       </c>
       <c r="AG32" t="s" s="2">
         <v>76</v>
@@ -6388,10 +6394,10 @@
     </row>
     <row r="33">
       <c r="A33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>287</v>
+        <v>289</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -6414,13 +6420,13 @@
         <v>19</v>
       </c>
       <c r="K33" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L33" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M33" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N33" s="2"/>
       <c r="O33" s="2"/>
@@ -6471,7 +6477,7 @@
         <v>19</v>
       </c>
       <c r="AF33" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG33" t="s" s="2">
         <v>76</v>
@@ -6480,7 +6486,7 @@
         <v>87</v>
       </c>
       <c r="AI33" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ33" t="s" s="2">
         <v>19</v>
@@ -6492,19 +6498,19 @@
         <v>19</v>
       </c>
       <c r="AM33" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>294</v>
+        <v>296</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E34" s="2"/>
       <c r="F34" t="s" s="2">
@@ -6526,13 +6532,13 @@
         <v>134</v>
       </c>
       <c r="L34" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M34" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N34" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O34" s="2"/>
       <c r="P34" t="s" s="2">
@@ -6582,7 +6588,7 @@
         <v>19</v>
       </c>
       <c r="AF34" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG34" t="s" s="2">
         <v>76</v>
@@ -6603,19 +6609,19 @@
         <v>19</v>
       </c>
       <c r="AM34" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>298</v>
+        <v>300</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E35" s="2"/>
       <c r="F35" t="s" s="2">
@@ -6637,16 +6643,16 @@
         <v>134</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N35" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O35" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -6695,7 +6701,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>76</v>
@@ -6721,10 +6727,10 @@
     </row>
     <row r="36">
       <c r="A36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6747,17 +6753,17 @@
         <v>19</v>
       </c>
       <c r="K36" t="s" s="2">
-        <v>304</v>
+        <v>306</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>305</v>
+        <v>307</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>306</v>
+        <v>308</v>
       </c>
       <c r="N36" s="2"/>
       <c r="O36" t="s" s="2">
-        <v>286</v>
+        <v>288</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6806,7 +6812,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>303</v>
+        <v>305</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>76</v>
@@ -6821,7 +6827,7 @@
         <v>99</v>
       </c>
       <c r="AK36" t="s" s="2">
-        <v>307</v>
+        <v>309</v>
       </c>
       <c r="AL36" t="s" s="2">
         <v>19</v>
@@ -6832,10 +6838,10 @@
     </row>
     <row r="37">
       <c r="A37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6858,19 +6864,19 @@
         <v>19</v>
       </c>
       <c r="K37" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>309</v>
+        <v>311</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>310</v>
+        <v>312</v>
       </c>
       <c r="N37" t="s" s="2">
-        <v>311</v>
+        <v>313</v>
       </c>
       <c r="O37" t="s" s="2">
-        <v>312</v>
+        <v>314</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6895,13 +6901,13 @@
         <v>19</v>
       </c>
       <c r="X37" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y37" t="s" s="2">
-        <v>313</v>
+        <v>315</v>
       </c>
       <c r="Z37" t="s" s="2">
-        <v>314</v>
+        <v>316</v>
       </c>
       <c r="AA37" t="s" s="2">
         <v>19</v>
@@ -6919,7 +6925,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>308</v>
+        <v>310</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>76</v>
@@ -6945,10 +6951,10 @@
     </row>
     <row r="38">
       <c r="A38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="C38" s="2"/>
       <c r="D38" t="s" s="2">
@@ -6971,19 +6977,19 @@
         <v>19</v>
       </c>
       <c r="K38" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>316</v>
+        <v>318</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>317</v>
+        <v>319</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>318</v>
+        <v>320</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>319</v>
+        <v>321</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -7032,7 +7038,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>315</v>
+        <v>317</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>76</v>
@@ -7058,10 +7064,10 @@
     </row>
     <row r="39">
       <c r="A39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -7084,17 +7090,17 @@
         <v>19</v>
       </c>
       <c r="K39" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L39" t="s" s="2">
-        <v>322</v>
+        <v>324</v>
       </c>
       <c r="M39" t="s" s="2">
-        <v>323</v>
+        <v>325</v>
       </c>
       <c r="N39" s="2"/>
       <c r="O39" t="s" s="2">
-        <v>324</v>
+        <v>326</v>
       </c>
       <c r="P39" t="s" s="2">
         <v>19</v>
@@ -7143,7 +7149,7 @@
         <v>19</v>
       </c>
       <c r="AF39" t="s" s="2">
-        <v>320</v>
+        <v>322</v>
       </c>
       <c r="AG39" t="s" s="2">
         <v>76</v>
@@ -7169,10 +7175,10 @@
     </row>
     <row r="40">
       <c r="A40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -7195,19 +7201,19 @@
         <v>19</v>
       </c>
       <c r="K40" t="s" s="2">
-        <v>321</v>
+        <v>323</v>
       </c>
       <c r="L40" t="s" s="2">
-        <v>326</v>
+        <v>328</v>
       </c>
       <c r="M40" t="s" s="2">
-        <v>327</v>
+        <v>329</v>
       </c>
       <c r="N40" t="s" s="2">
-        <v>328</v>
+        <v>330</v>
       </c>
       <c r="O40" t="s" s="2">
-        <v>329</v>
+        <v>331</v>
       </c>
       <c r="P40" t="s" s="2">
         <v>19</v>
@@ -7256,7 +7262,7 @@
         <v>19</v>
       </c>
       <c r="AF40" t="s" s="2">
-        <v>325</v>
+        <v>327</v>
       </c>
       <c r="AG40" t="s" s="2">
         <v>76</v>
@@ -7282,10 +7288,10 @@
     </row>
     <row r="41">
       <c r="A41" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -7308,19 +7314,19 @@
         <v>19</v>
       </c>
       <c r="K41" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L41" t="s" s="2">
-        <v>331</v>
+        <v>333</v>
       </c>
       <c r="M41" t="s" s="2">
-        <v>332</v>
+        <v>334</v>
       </c>
       <c r="N41" t="s" s="2">
-        <v>333</v>
+        <v>335</v>
       </c>
       <c r="O41" t="s" s="2">
-        <v>334</v>
+        <v>336</v>
       </c>
       <c r="P41" t="s" s="2">
         <v>19</v>
@@ -7369,7 +7375,7 @@
         <v>19</v>
       </c>
       <c r="AF41" t="s" s="2">
-        <v>330</v>
+        <v>332</v>
       </c>
       <c r="AG41" t="s" s="2">
         <v>76</v>
@@ -7395,10 +7401,10 @@
     </row>
     <row r="42">
       <c r="A42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>335</v>
+        <v>337</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -7421,13 +7427,13 @@
         <v>19</v>
       </c>
       <c r="K42" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" s="2"/>
@@ -7478,7 +7484,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>76</v>
@@ -7487,7 +7493,7 @@
         <v>87</v>
       </c>
       <c r="AI42" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ42" t="s" s="2">
         <v>19</v>
@@ -7499,19 +7505,19 @@
         <v>19</v>
       </c>
       <c r="AM42" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>336</v>
+        <v>338</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E43" s="2"/>
       <c r="F43" t="s" s="2">
@@ -7533,13 +7539,13 @@
         <v>134</v>
       </c>
       <c r="L43" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M43" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N43" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O43" s="2"/>
       <c r="P43" t="s" s="2">
@@ -7589,7 +7595,7 @@
         <v>19</v>
       </c>
       <c r="AF43" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG43" t="s" s="2">
         <v>76</v>
@@ -7610,19 +7616,19 @@
         <v>19</v>
       </c>
       <c r="AM43" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>337</v>
+        <v>339</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E44" s="2"/>
       <c r="F44" t="s" s="2">
@@ -7644,16 +7650,16 @@
         <v>134</v>
       </c>
       <c r="L44" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M44" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N44" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O44" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P44" t="s" s="2">
         <v>19</v>
@@ -7702,7 +7708,7 @@
         <v>19</v>
       </c>
       <c r="AF44" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG44" t="s" s="2">
         <v>76</v>
@@ -7728,10 +7734,10 @@
     </row>
     <row r="45">
       <c r="A45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7754,17 +7760,17 @@
         <v>19</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>339</v>
+        <v>341</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>340</v>
+        <v>342</v>
       </c>
       <c r="N45" s="2"/>
       <c r="O45" t="s" s="2">
-        <v>341</v>
+        <v>343</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7789,13 +7795,13 @@
         <v>19</v>
       </c>
       <c r="X45" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y45" t="s" s="2">
-        <v>342</v>
+        <v>344</v>
       </c>
       <c r="Z45" t="s" s="2">
-        <v>343</v>
+        <v>345</v>
       </c>
       <c r="AA45" t="s" s="2">
         <v>19</v>
@@ -7813,7 +7819,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>338</v>
+        <v>340</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>87</v>
@@ -7839,10 +7845,10 @@
     </row>
     <row r="46">
       <c r="A46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7865,19 +7871,19 @@
         <v>19</v>
       </c>
       <c r="K46" t="s" s="2">
-        <v>345</v>
+        <v>347</v>
       </c>
       <c r="L46" t="s" s="2">
-        <v>346</v>
+        <v>348</v>
       </c>
       <c r="M46" t="s" s="2">
-        <v>347</v>
+        <v>349</v>
       </c>
       <c r="N46" t="s" s="2">
-        <v>348</v>
+        <v>350</v>
       </c>
       <c r="O46" t="s" s="2">
-        <v>349</v>
+        <v>351</v>
       </c>
       <c r="P46" t="s" s="2">
         <v>19</v>
@@ -7926,7 +7932,7 @@
         <v>19</v>
       </c>
       <c r="AF46" t="s" s="2">
-        <v>344</v>
+        <v>346</v>
       </c>
       <c r="AG46" t="s" s="2">
         <v>76</v>
@@ -7952,10 +7958,10 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7978,19 +7984,19 @@
         <v>19</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>351</v>
+        <v>353</v>
       </c>
       <c r="L47" t="s" s="2">
-        <v>352</v>
+        <v>354</v>
       </c>
       <c r="M47" t="s" s="2">
-        <v>353</v>
+        <v>355</v>
       </c>
       <c r="N47" t="s" s="2">
-        <v>354</v>
+        <v>356</v>
       </c>
       <c r="O47" t="s" s="2">
-        <v>355</v>
+        <v>357</v>
       </c>
       <c r="P47" t="s" s="2">
         <v>19</v>
@@ -8039,7 +8045,7 @@
         <v>19</v>
       </c>
       <c r="AF47" t="s" s="2">
-        <v>350</v>
+        <v>352</v>
       </c>
       <c r="AG47" t="s" s="2">
         <v>76</v>
@@ -8057,7 +8063,7 @@
         <v>19</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>356</v>
+        <v>358</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>19</v>
@@ -8065,10 +8071,10 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -8076,7 +8082,7 @@
       </c>
       <c r="E48" s="2"/>
       <c r="F48" t="s" s="2">
-        <v>358</v>
+        <v>360</v>
       </c>
       <c r="G48" t="s" s="2">
         <v>77</v>
@@ -8091,19 +8097,19 @@
         <v>19</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -8150,7 +8156,7 @@
         <v>138</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>76</v>
@@ -8176,13 +8182,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>364</v>
+        <v>366</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>365</v>
+        <v>367</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>19</v>
@@ -8204,19 +8210,19 @@
         <v>19</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>366</v>
+        <v>368</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>367</v>
+        <v>369</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O49" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P49" t="s" s="2">
         <v>19</v>
@@ -8265,7 +8271,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>76</v>
@@ -8291,13 +8297,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>368</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>369</v>
+        <v>371</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>19</v>
@@ -8319,19 +8325,19 @@
         <v>19</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>370</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N50" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O50" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -8380,7 +8386,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>357</v>
+        <v>359</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>76</v>
@@ -8406,10 +8412,10 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -8432,17 +8438,17 @@
         <v>19</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>374</v>
+        <v>376</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>376</v>
+        <v>378</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -8491,7 +8497,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>372</v>
+        <v>374</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>76</v>
@@ -8509,7 +8515,7 @@
         <v>19</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>19</v>
@@ -8517,10 +8523,10 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8543,19 +8549,19 @@
         <v>19</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>379</v>
+        <v>381</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>380</v>
+        <v>382</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>381</v>
+        <v>383</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>382</v>
+        <v>384</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8584,7 +8590,7 @@
       </c>
       <c r="Y52" s="2"/>
       <c r="Z52" t="s" s="2">
-        <v>383</v>
+        <v>385</v>
       </c>
       <c r="AA52" t="s" s="2">
         <v>19</v>
@@ -8602,7 +8608,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>76</v>
@@ -8628,10 +8634,10 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8654,13 +8660,13 @@
         <v>19</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>385</v>
+        <v>387</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>386</v>
+        <v>388</v>
       </c>
       <c r="N53" s="2"/>
       <c r="O53" s="2"/>
@@ -8711,7 +8717,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>384</v>
+        <v>386</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>76</v>
@@ -8737,10 +8743,10 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>387</v>
+        <v>389</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8763,13 +8769,13 @@
         <v>19</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N54" s="2"/>
       <c r="O54" s="2"/>
@@ -8820,7 +8826,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>76</v>
@@ -8829,7 +8835,7 @@
         <v>87</v>
       </c>
       <c r="AI54" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ54" t="s" s="2">
         <v>19</v>
@@ -8841,19 +8847,19 @@
         <v>19</v>
       </c>
       <c r="AM54" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>388</v>
+        <v>390</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E55" s="2"/>
       <c r="F55" t="s" s="2">
@@ -8875,13 +8881,13 @@
         <v>134</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N55" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O55" s="2"/>
       <c r="P55" t="s" s="2">
@@ -8931,7 +8937,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>76</v>
@@ -8952,19 +8958,19 @@
         <v>19</v>
       </c>
       <c r="AM55" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>389</v>
+        <v>391</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E56" s="2"/>
       <c r="F56" t="s" s="2">
@@ -8986,16 +8992,16 @@
         <v>134</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -9044,7 +9050,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>76</v>
@@ -9070,10 +9076,10 @@
     </row>
     <row r="57">
       <c r="A57" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9096,13 +9102,13 @@
         <v>19</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>391</v>
+        <v>393</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>392</v>
+        <v>394</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" s="2"/>
@@ -9129,11 +9135,11 @@
         <v>19</v>
       </c>
       <c r="X57" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y57" s="2"/>
       <c r="Z57" t="s" s="2">
-        <v>393</v>
+        <v>395</v>
       </c>
       <c r="AA57" t="s" s="2">
         <v>19</v>
@@ -9151,7 +9157,7 @@
         <v>19</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>390</v>
+        <v>392</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>87</v>
@@ -9177,10 +9183,10 @@
     </row>
     <row r="58">
       <c r="A58" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9203,13 +9209,13 @@
         <v>19</v>
       </c>
       <c r="K58" t="s" s="2">
-        <v>395</v>
+        <v>397</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>396</v>
+        <v>398</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="N58" s="2"/>
       <c r="O58" s="2"/>
@@ -9260,7 +9266,7 @@
         <v>19</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>394</v>
+        <v>396</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>87</v>
@@ -9286,10 +9292,10 @@
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9312,17 +9318,17 @@
         <v>19</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>399</v>
+        <v>401</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>400</v>
+        <v>402</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" t="s" s="2">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="P59" t="s" s="2">
         <v>19</v>
@@ -9371,7 +9377,7 @@
         <v>19</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>398</v>
+        <v>400</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>76</v>
@@ -9397,10 +9403,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9423,13 +9429,13 @@
         <v>19</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -9480,7 +9486,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>76</v>
@@ -9489,7 +9495,7 @@
         <v>87</v>
       </c>
       <c r="AI60" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ60" t="s" s="2">
         <v>19</v>
@@ -9501,19 +9507,19 @@
         <v>19</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9535,13 +9541,13 @@
         <v>134</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O61" s="2"/>
       <c r="P61" t="s" s="2">
@@ -9591,7 +9597,7 @@
         <v>19</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>76</v>
@@ -9612,19 +9618,19 @@
         <v>19</v>
       </c>
       <c r="AM61" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E62" s="2"/>
       <c r="F62" t="s" s="2">
@@ -9646,16 +9652,16 @@
         <v>134</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O62" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P62" t="s" s="2">
         <v>19</v>
@@ -9704,7 +9710,7 @@
         <v>19</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>76</v>
@@ -9730,10 +9736,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9756,17 +9762,17 @@
         <v>19</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -9815,7 +9821,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>405</v>
+        <v>407</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>87</v>
@@ -9841,10 +9847,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9867,17 +9873,17 @@
         <v>19</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>19</v>
@@ -9926,7 +9932,7 @@
         <v>19</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>87</v>
@@ -9944,7 +9950,7 @@
         <v>19</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>19</v>
@@ -9952,10 +9958,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9978,19 +9984,19 @@
         <v>19</v>
       </c>
       <c r="K65" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N65" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="O65" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>19</v>
@@ -10039,7 +10045,7 @@
         <v>19</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>76</v>
@@ -10065,10 +10071,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10091,19 +10097,19 @@
         <v>19</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -10128,13 +10134,13 @@
         <v>19</v>
       </c>
       <c r="X66" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y66" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="Z66" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AA66" t="s" s="2">
         <v>19</v>
@@ -10152,7 +10158,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>76</v>
@@ -10178,10 +10184,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10204,17 +10210,17 @@
         <v>19</v>
       </c>
       <c r="K67" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="N67" s="2"/>
       <c r="O67" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="P67" t="s" s="2">
         <v>19</v>
@@ -10239,11 +10245,11 @@
         <v>19</v>
       </c>
       <c r="X67" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y67" s="2"/>
       <c r="Z67" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="AA67" t="s" s="2">
         <v>19</v>
@@ -10261,7 +10267,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>76</v>
@@ -10287,14 +10293,14 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="E68" s="2"/>
       <c r="F68" t="s" s="2">
@@ -10313,19 +10319,19 @@
         <v>19</v>
       </c>
       <c r="K68" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="N68" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="O68" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -10374,7 +10380,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>76</v>
@@ -10389,7 +10395,7 @@
         <v>99</v>
       </c>
       <c r="AK68" t="s" s="2">
-        <v>440</v>
+        <v>442</v>
       </c>
       <c r="AL68" t="s" s="2">
         <v>19</v>
@@ -10400,10 +10406,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>441</v>
+        <v>443</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10426,13 +10432,13 @@
         <v>19</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10483,7 +10489,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>76</v>
@@ -10492,7 +10498,7 @@
         <v>87</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>19</v>
@@ -10504,19 +10510,19 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>442</v>
+        <v>444</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E70" s="2"/>
       <c r="F70" t="s" s="2">
@@ -10538,13 +10544,13 @@
         <v>134</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O70" s="2"/>
       <c r="P70" t="s" s="2">
@@ -10594,7 +10600,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>76</v>
@@ -10615,19 +10621,19 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>443</v>
+        <v>445</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E71" s="2"/>
       <c r="F71" t="s" s="2">
@@ -10649,16 +10655,16 @@
         <v>134</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10707,7 +10713,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>76</v>
@@ -10733,10 +10739,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10759,17 +10765,17 @@
         <v>19</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>445</v>
+        <v>447</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>446</v>
+        <v>448</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" t="s" s="2">
-        <v>447</v>
+        <v>449</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10818,7 +10824,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>444</v>
+        <v>446</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>87</v>
@@ -10844,10 +10850,10 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10870,19 +10876,19 @@
         <v>19</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>449</v>
+        <v>451</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>450</v>
+        <v>452</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>451</v>
+        <v>453</v>
       </c>
       <c r="O73" t="s" s="2">
-        <v>452</v>
+        <v>454</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -10907,13 +10913,13 @@
         <v>19</v>
       </c>
       <c r="X73" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y73" t="s" s="2">
-        <v>453</v>
+        <v>455</v>
       </c>
       <c r="Z73" t="s" s="2">
-        <v>454</v>
+        <v>456</v>
       </c>
       <c r="AA73" t="s" s="2">
         <v>19</v>
@@ -10931,7 +10937,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>448</v>
+        <v>450</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>87</v>
@@ -10957,10 +10963,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10983,17 +10989,17 @@
         <v>19</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>456</v>
+        <v>458</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>457</v>
+        <v>459</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -11018,13 +11024,13 @@
         <v>19</v>
       </c>
       <c r="X74" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y74" t="s" s="2">
-        <v>459</v>
+        <v>461</v>
       </c>
       <c r="Z74" t="s" s="2">
-        <v>460</v>
+        <v>462</v>
       </c>
       <c r="AA74" t="s" s="2">
         <v>19</v>
@@ -11042,7 +11048,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>455</v>
+        <v>457</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>76</v>
@@ -11068,10 +11074,10 @@
     </row>
     <row r="75">
       <c r="A75" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11094,13 +11100,13 @@
         <v>19</v>
       </c>
       <c r="K75" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>463</v>
+        <v>465</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>464</v>
+        <v>466</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" s="2"/>
@@ -11151,7 +11157,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>461</v>
+        <v>463</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>76</v>
@@ -11177,10 +11183,10 @@
     </row>
     <row r="76">
       <c r="A76" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11203,19 +11209,19 @@
         <v>19</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>466</v>
+        <v>468</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>467</v>
+        <v>469</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>469</v>
+        <v>471</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>470</v>
+        <v>472</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -11264,7 +11270,7 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>465</v>
+        <v>467</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>76</v>
@@ -11290,10 +11296,10 @@
     </row>
     <row r="77">
       <c r="A77" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11316,19 +11322,19 @@
         <v>19</v>
       </c>
       <c r="K77" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>472</v>
+        <v>474</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>473</v>
+        <v>475</v>
       </c>
       <c r="N77" t="s" s="2">
-        <v>474</v>
+        <v>476</v>
       </c>
       <c r="O77" t="s" s="2">
-        <v>475</v>
+        <v>477</v>
       </c>
       <c r="P77" t="s" s="2">
         <v>19</v>
@@ -11353,13 +11359,13 @@
         <v>19</v>
       </c>
       <c r="X77" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y77" t="s" s="2">
-        <v>476</v>
+        <v>478</v>
       </c>
       <c r="Z77" t="s" s="2">
-        <v>477</v>
+        <v>479</v>
       </c>
       <c r="AA77" t="s" s="2">
         <v>19</v>
@@ -11377,7 +11383,7 @@
         <v>19</v>
       </c>
       <c r="AF77" t="s" s="2">
-        <v>471</v>
+        <v>473</v>
       </c>
       <c r="AG77" t="s" s="2">
         <v>76</v>
@@ -11403,10 +11409,10 @@
     </row>
     <row r="78">
       <c r="A78" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11429,17 +11435,17 @@
         <v>19</v>
       </c>
       <c r="K78" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L78" t="s" s="2">
-        <v>479</v>
+        <v>481</v>
       </c>
       <c r="M78" t="s" s="2">
-        <v>480</v>
+        <v>482</v>
       </c>
       <c r="N78" s="2"/>
       <c r="O78" t="s" s="2">
-        <v>481</v>
+        <v>483</v>
       </c>
       <c r="P78" t="s" s="2">
         <v>19</v>
@@ -11488,7 +11494,7 @@
         <v>19</v>
       </c>
       <c r="AF78" t="s" s="2">
-        <v>478</v>
+        <v>480</v>
       </c>
       <c r="AG78" t="s" s="2">
         <v>76</v>
@@ -11503,7 +11509,7 @@
         <v>99</v>
       </c>
       <c r="AK78" t="s" s="2">
-        <v>482</v>
+        <v>484</v>
       </c>
       <c r="AL78" t="s" s="2">
         <v>19</v>
@@ -11514,10 +11520,10 @@
     </row>
     <row r="79">
       <c r="A79" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>483</v>
+        <v>485</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11540,13 +11546,13 @@
         <v>19</v>
       </c>
       <c r="K79" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L79" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M79" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N79" s="2"/>
       <c r="O79" s="2"/>
@@ -11597,7 +11603,7 @@
         <v>19</v>
       </c>
       <c r="AF79" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG79" t="s" s="2">
         <v>76</v>
@@ -11606,7 +11612,7 @@
         <v>87</v>
       </c>
       <c r="AI79" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ79" t="s" s="2">
         <v>19</v>
@@ -11618,19 +11624,19 @@
         <v>19</v>
       </c>
       <c r="AM79" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>484</v>
+        <v>486</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E80" s="2"/>
       <c r="F80" t="s" s="2">
@@ -11652,13 +11658,13 @@
         <v>134</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11708,7 +11714,7 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>76</v>
@@ -11729,19 +11735,19 @@
         <v>19</v>
       </c>
       <c r="AM80" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>485</v>
+        <v>487</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E81" s="2"/>
       <c r="F81" t="s" s="2">
@@ -11763,16 +11769,16 @@
         <v>134</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>19</v>
@@ -11821,7 +11827,7 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>76</v>
@@ -11847,10 +11853,10 @@
     </row>
     <row r="82">
       <c r="A82" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11873,19 +11879,19 @@
         <v>19</v>
       </c>
       <c r="K82" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>487</v>
+        <v>489</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>488</v>
+        <v>490</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>489</v>
+        <v>491</v>
       </c>
       <c r="O82" t="s" s="2">
-        <v>490</v>
+        <v>492</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>19</v>
@@ -11934,7 +11940,7 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>486</v>
+        <v>488</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>87</v>
@@ -11960,10 +11966,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11986,17 +11992,17 @@
         <v>19</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>492</v>
+        <v>494</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>493</v>
+        <v>495</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>494</v>
+        <v>496</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>495</v>
+        <v>497</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
@@ -12021,13 +12027,13 @@
         <v>19</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y83" t="s" s="2">
-        <v>496</v>
+        <v>498</v>
       </c>
       <c r="Z83" t="s" s="2">
-        <v>497</v>
+        <v>499</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>19</v>
@@ -12045,7 +12051,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>491</v>
+        <v>493</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>87</v>
@@ -12071,10 +12077,10 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -12097,19 +12103,19 @@
         <v>19</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>499</v>
+        <v>501</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="O84" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>19</v>
@@ -12134,13 +12140,13 @@
         <v>19</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y84" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="Z84" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
@@ -12158,7 +12164,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>498</v>
+        <v>500</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>76</v>
@@ -12184,10 +12190,10 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12210,17 +12216,17 @@
         <v>19</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="N85" s="2"/>
       <c r="O85" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>19</v>
@@ -12245,13 +12251,13 @@
         <v>19</v>
       </c>
       <c r="X85" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y85" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="Z85" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="AA85" t="s" s="2">
         <v>19</v>
@@ -12269,7 +12275,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>76</v>
@@ -12295,10 +12301,10 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12321,17 +12327,17 @@
         <v>19</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -12380,7 +12386,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>76</v>
@@ -12406,10 +12412,10 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12432,13 +12438,13 @@
         <v>19</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12489,7 +12495,7 @@
         <v>19</v>
       </c>
       <c r="AF87" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG87" t="s" s="2">
         <v>76</v>
@@ -12498,7 +12504,7 @@
         <v>87</v>
       </c>
       <c r="AI87" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ87" t="s" s="2">
         <v>19</v>
@@ -12510,15 +12516,15 @@
         <v>19</v>
       </c>
       <c r="AM87" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12596,7 +12602,7 @@
         <v>138</v>
       </c>
       <c r="AF88" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG88" t="s" s="2">
         <v>76</v>
@@ -12622,13 +12628,13 @@
     </row>
     <row r="89">
       <c r="A89" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="C89" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="D89" t="s" s="2">
         <v>19</v>
@@ -12650,13 +12656,13 @@
         <v>19</v>
       </c>
       <c r="K89" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N89" s="2"/>
       <c r="O89" s="2"/>
@@ -12707,7 +12713,7 @@
         <v>19</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>76</v>
@@ -12733,14 +12739,14 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E90" s="2"/>
       <c r="F90" t="s" s="2">
@@ -12762,16 +12768,16 @@
         <v>134</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -12820,7 +12826,7 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>76</v>
@@ -12846,10 +12852,10 @@
     </row>
     <row r="91">
       <c r="A91" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12872,17 +12878,17 @@
         <v>19</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>19</v>
@@ -12931,7 +12937,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>87</v>
@@ -12957,10 +12963,10 @@
     </row>
     <row r="92">
       <c r="A92" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12983,19 +12989,19 @@
         <v>19</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
@@ -13020,13 +13026,13 @@
         <v>19</v>
       </c>
       <c r="X92" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>19</v>
@@ -13044,7 +13050,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>76</v>
@@ -13070,10 +13076,10 @@
     </row>
     <row r="93">
       <c r="A93" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -13096,17 +13102,17 @@
         <v>19</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>241</v>
+        <v>243</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
@@ -13155,7 +13161,7 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>76</v>
@@ -13181,10 +13187,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13207,17 +13213,17 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -13242,13 +13248,13 @@
         <v>19</v>
       </c>
       <c r="X94" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y94" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="Z94" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="AA94" t="s" s="2">
         <v>19</v>
@@ -13266,7 +13272,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>87</v>
@@ -13292,10 +13298,10 @@
     </row>
     <row r="95">
       <c r="A95" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13318,17 +13324,17 @@
         <v>19</v>
       </c>
       <c r="K95" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P95" t="s" s="2">
         <v>19</v>
@@ -13377,7 +13383,7 @@
         <v>19</v>
       </c>
       <c r="AF95" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="AG95" t="s" s="2">
         <v>76</v>
@@ -13403,10 +13409,10 @@
     </row>
     <row r="96">
       <c r="A96" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13429,19 +13435,19 @@
         <v>88</v>
       </c>
       <c r="K96" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="N96" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="O96" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="P96" t="s" s="2">
         <v>19</v>
@@ -13490,7 +13496,7 @@
         <v>19</v>
       </c>
       <c r="AF96" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="AG96" t="s" s="2">
         <v>76</v>
@@ -13511,15 +13517,15 @@
         <v>19</v>
       </c>
       <c r="AM96" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B97" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="C97" s="2"/>
       <c r="D97" t="s" s="2">
@@ -13542,13 +13548,13 @@
         <v>19</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -13599,7 +13605,7 @@
         <v>19</v>
       </c>
       <c r="AF97" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG97" t="s" s="2">
         <v>76</v>
@@ -13608,7 +13614,7 @@
         <v>87</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ97" t="s" s="2">
         <v>19</v>
@@ -13620,19 +13626,19 @@
         <v>19</v>
       </c>
       <c r="AM97" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E98" s="2"/>
       <c r="F98" t="s" s="2">
@@ -13654,13 +13660,13 @@
         <v>134</v>
       </c>
       <c r="L98" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M98" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N98" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O98" s="2"/>
       <c r="P98" t="s" s="2">
@@ -13710,7 +13716,7 @@
         <v>19</v>
       </c>
       <c r="AF98" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG98" t="s" s="2">
         <v>76</v>
@@ -13731,19 +13737,19 @@
         <v>19</v>
       </c>
       <c r="AM98" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E99" s="2"/>
       <c r="F99" t="s" s="2">
@@ -13765,16 +13771,16 @@
         <v>134</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N99" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O99" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P99" t="s" s="2">
         <v>19</v>
@@ -13823,7 +13829,7 @@
         <v>19</v>
       </c>
       <c r="AF99" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG99" t="s" s="2">
         <v>76</v>
@@ -13849,10 +13855,10 @@
     </row>
     <row r="100">
       <c r="A100" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -13875,17 +13881,17 @@
         <v>88</v>
       </c>
       <c r="K100" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="N100" s="2"/>
       <c r="O100" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="P100" t="s" s="2">
         <v>19</v>
@@ -13934,7 +13940,7 @@
         <v>19</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>87</v>
@@ -13960,10 +13966,10 @@
     </row>
     <row r="101">
       <c r="A101" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -13986,19 +13992,19 @@
         <v>88</v>
       </c>
       <c r="K101" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N101" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="O101" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="P101" t="s" s="2">
         <v>19</v>
@@ -14047,7 +14053,7 @@
         <v>19</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>87</v>
@@ -14073,10 +14079,10 @@
     </row>
     <row r="102">
       <c r="A102" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="C102" s="2"/>
       <c r="D102" t="s" s="2">
@@ -14099,19 +14105,19 @@
         <v>19</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="N102" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="O102" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="P102" t="s" s="2">
         <v>19</v>
@@ -14160,7 +14166,7 @@
         <v>19</v>
       </c>
       <c r="AF102" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="AG102" t="s" s="2">
         <v>76</v>
@@ -14175,10 +14181,10 @@
         <v>99</v>
       </c>
       <c r="AK102" t="s" s="2">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>19</v>
@@ -14186,10 +14192,10 @@
     </row>
     <row r="103">
       <c r="A103" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14212,17 +14218,17 @@
         <v>88</v>
       </c>
       <c r="K103" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="L103" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="M103" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="N103" s="2"/>
       <c r="O103" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P103" t="s" s="2">
         <v>19</v>
@@ -14271,7 +14277,7 @@
         <v>19</v>
       </c>
       <c r="AF103" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG103" t="s" s="2">
         <v>87</v>
@@ -14297,10 +14303,10 @@
     </row>
     <row r="104">
       <c r="A104" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14323,17 +14329,17 @@
         <v>19</v>
       </c>
       <c r="K104" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="P104" t="s" s="2">
         <v>19</v>
@@ -14382,7 +14388,7 @@
         <v>19</v>
       </c>
       <c r="AF104" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AG104" t="s" s="2">
         <v>76</v>
@@ -14408,10 +14414,10 @@
     </row>
     <row r="105">
       <c r="A105" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14434,19 +14440,19 @@
         <v>19</v>
       </c>
       <c r="K105" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="O105" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="P105" t="s" s="2">
         <v>19</v>
@@ -14495,7 +14501,7 @@
         <v>19</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>76</v>
@@ -14521,10 +14527,10 @@
     </row>
     <row r="106">
       <c r="A106" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -14547,19 +14553,19 @@
         <v>19</v>
       </c>
       <c r="K106" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="N106" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="O106" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="P106" t="s" s="2">
         <v>19</v>
@@ -14608,7 +14614,7 @@
         <v>19</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>76</v>
@@ -14634,10 +14640,10 @@
     </row>
     <row r="107">
       <c r="A107" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -14660,17 +14666,17 @@
         <v>19</v>
       </c>
       <c r="K107" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>593</v>
+        <v>595</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" t="s" s="2">
-        <v>594</v>
+        <v>596</v>
       </c>
       <c r="P107" t="s" s="2">
         <v>19</v>
@@ -14719,7 +14725,7 @@
         <v>19</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>76</v>
@@ -14745,10 +14751,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>595</v>
+        <v>597</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -14771,13 +14777,13 @@
         <v>19</v>
       </c>
       <c r="K108" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N108" s="2"/>
       <c r="O108" s="2"/>
@@ -14828,7 +14834,7 @@
         <v>19</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>76</v>
@@ -14837,7 +14843,7 @@
         <v>87</v>
       </c>
       <c r="AI108" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ108" t="s" s="2">
         <v>19</v>
@@ -14849,19 +14855,19 @@
         <v>19</v>
       </c>
       <c r="AM108" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>596</v>
+        <v>598</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E109" s="2"/>
       <c r="F109" t="s" s="2">
@@ -14883,13 +14889,13 @@
         <v>134</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O109" s="2"/>
       <c r="P109" t="s" s="2">
@@ -14939,7 +14945,7 @@
         <v>19</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>76</v>
@@ -14960,19 +14966,19 @@
         <v>19</v>
       </c>
       <c r="AM109" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E110" s="2"/>
       <c r="F110" t="s" s="2">
@@ -14994,16 +15000,16 @@
         <v>134</v>
       </c>
       <c r="L110" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M110" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N110" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O110" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P110" t="s" s="2">
         <v>19</v>
@@ -15052,7 +15058,7 @@
         <v>19</v>
       </c>
       <c r="AF110" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG110" t="s" s="2">
         <v>76</v>
@@ -15078,10 +15084,10 @@
     </row>
     <row r="111">
       <c r="A111" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15104,19 +15110,19 @@
         <v>19</v>
       </c>
       <c r="K111" t="s" s="2">
-        <v>599</v>
+        <v>601</v>
       </c>
       <c r="L111" t="s" s="2">
-        <v>600</v>
+        <v>602</v>
       </c>
       <c r="M111" t="s" s="2">
-        <v>601</v>
+        <v>603</v>
       </c>
       <c r="N111" t="s" s="2">
-        <v>602</v>
+        <v>604</v>
       </c>
       <c r="O111" t="s" s="2">
-        <v>603</v>
+        <v>605</v>
       </c>
       <c r="P111" t="s" s="2">
         <v>19</v>
@@ -15165,7 +15171,7 @@
         <v>19</v>
       </c>
       <c r="AF111" t="s" s="2">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="AG111" t="s" s="2">
         <v>87</v>
@@ -15191,10 +15197,10 @@
     </row>
     <row r="112">
       <c r="A112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
@@ -15217,17 +15223,17 @@
         <v>19</v>
       </c>
       <c r="K112" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>605</v>
+        <v>607</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>606</v>
+        <v>608</v>
       </c>
       <c r="N112" s="2"/>
       <c r="O112" t="s" s="2">
-        <v>607</v>
+        <v>609</v>
       </c>
       <c r="P112" t="s" s="2">
         <v>19</v>
@@ -15252,13 +15258,13 @@
         <v>19</v>
       </c>
       <c r="X112" t="s" s="2">
-        <v>208</v>
+        <v>210</v>
       </c>
       <c r="Y112" t="s" s="2">
-        <v>608</v>
+        <v>610</v>
       </c>
       <c r="Z112" t="s" s="2">
-        <v>609</v>
+        <v>611</v>
       </c>
       <c r="AA112" t="s" s="2">
         <v>19</v>
@@ -15276,7 +15282,7 @@
         <v>19</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>604</v>
+        <v>606</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>76</v>
@@ -15302,10 +15308,10 @@
     </row>
     <row r="113">
       <c r="A113" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15328,17 +15334,17 @@
         <v>19</v>
       </c>
       <c r="K113" t="s" s="2">
-        <v>611</v>
+        <v>613</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>612</v>
+        <v>614</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>613</v>
+        <v>615</v>
       </c>
       <c r="N113" s="2"/>
       <c r="O113" t="s" s="2">
-        <v>614</v>
+        <v>616</v>
       </c>
       <c r="P113" t="s" s="2">
         <v>19</v>
@@ -15387,7 +15393,7 @@
         <v>19</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>610</v>
+        <v>612</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>76</v>
@@ -15413,10 +15419,10 @@
     </row>
     <row r="114">
       <c r="A114" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15439,17 +15445,17 @@
         <v>19</v>
       </c>
       <c r="K114" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="P114" t="s" s="2">
         <v>19</v>
@@ -15498,7 +15504,7 @@
         <v>19</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>615</v>
+        <v>617</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>76</v>
@@ -15524,10 +15530,10 @@
     </row>
     <row r="115">
       <c r="A115" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -15550,17 +15556,17 @@
         <v>19</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>622</v>
+        <v>624</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="P115" t="s" s="2">
         <v>19</v>
@@ -15609,7 +15615,7 @@
         <v>19</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>620</v>
+        <v>622</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>76</v>
@@ -15635,10 +15641,10 @@
     </row>
     <row r="116">
       <c r="A116" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>624</v>
+        <v>626</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -15661,13 +15667,13 @@
         <v>19</v>
       </c>
       <c r="K116" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N116" s="2"/>
       <c r="O116" s="2"/>
@@ -15718,7 +15724,7 @@
         <v>19</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>76</v>
@@ -15727,7 +15733,7 @@
         <v>87</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>19</v>
@@ -15739,19 +15745,19 @@
         <v>19</v>
       </c>
       <c r="AM116" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>625</v>
+        <v>627</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E117" s="2"/>
       <c r="F117" t="s" s="2">
@@ -15773,13 +15779,13 @@
         <v>134</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
@@ -15829,7 +15835,7 @@
         <v>19</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>76</v>
@@ -15850,19 +15856,19 @@
         <v>19</v>
       </c>
       <c r="AM117" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E118" s="2"/>
       <c r="F118" t="s" s="2">
@@ -15884,16 +15890,16 @@
         <v>134</v>
       </c>
       <c r="L118" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M118" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N118" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O118" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P118" t="s" s="2">
         <v>19</v>
@@ -15942,7 +15948,7 @@
         <v>19</v>
       </c>
       <c r="AF118" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG118" t="s" s="2">
         <v>76</v>
@@ -15968,10 +15974,10 @@
     </row>
     <row r="119">
       <c r="A119" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -15994,17 +16000,17 @@
         <v>19</v>
       </c>
       <c r="K119" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N119" s="2"/>
       <c r="O119" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>19</v>
@@ -16053,7 +16059,7 @@
         <v>19</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>627</v>
+        <v>629</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>87</v>
@@ -16079,10 +16085,10 @@
     </row>
     <row r="120">
       <c r="A120" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16105,17 +16111,17 @@
         <v>19</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N120" s="2"/>
       <c r="O120" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P120" t="s" s="2">
         <v>19</v>
@@ -16164,7 +16170,7 @@
         <v>19</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>631</v>
+        <v>633</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>76</v>
@@ -16190,10 +16196,10 @@
     </row>
     <row r="121">
       <c r="A121" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16216,17 +16222,17 @@
         <v>19</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>633</v>
+        <v>635</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>634</v>
+        <v>636</v>
       </c>
       <c r="N121" s="2"/>
       <c r="O121" t="s" s="2">
-        <v>635</v>
+        <v>637</v>
       </c>
       <c r="P121" t="s" s="2">
         <v>19</v>
@@ -16275,7 +16281,7 @@
         <v>19</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>632</v>
+        <v>634</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>76</v>
@@ -16301,10 +16307,10 @@
     </row>
     <row r="122">
       <c r="A122" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16327,17 +16333,17 @@
         <v>19</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>637</v>
+        <v>639</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>638</v>
+        <v>640</v>
       </c>
       <c r="N122" s="2"/>
       <c r="O122" t="s" s="2">
-        <v>639</v>
+        <v>641</v>
       </c>
       <c r="P122" t="s" s="2">
         <v>19</v>
@@ -16386,7 +16392,7 @@
         <v>19</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>636</v>
+        <v>638</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>76</v>
@@ -16412,10 +16418,10 @@
     </row>
     <row r="123">
       <c r="A123" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -16438,17 +16444,17 @@
         <v>19</v>
       </c>
       <c r="K123" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L123" t="s" s="2">
-        <v>641</v>
+        <v>643</v>
       </c>
       <c r="M123" t="s" s="2">
-        <v>642</v>
+        <v>644</v>
       </c>
       <c r="N123" s="2"/>
       <c r="O123" t="s" s="2">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="P123" t="s" s="2">
         <v>19</v>
@@ -16497,7 +16503,7 @@
         <v>19</v>
       </c>
       <c r="AF123" t="s" s="2">
-        <v>640</v>
+        <v>642</v>
       </c>
       <c r="AG123" t="s" s="2">
         <v>76</v>
@@ -16523,10 +16529,10 @@
     </row>
     <row r="124">
       <c r="A124" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -16549,17 +16555,17 @@
         <v>19</v>
       </c>
       <c r="K124" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L124" t="s" s="2">
-        <v>645</v>
+        <v>647</v>
       </c>
       <c r="M124" t="s" s="2">
-        <v>646</v>
+        <v>648</v>
       </c>
       <c r="N124" s="2"/>
       <c r="O124" t="s" s="2">
-        <v>647</v>
+        <v>649</v>
       </c>
       <c r="P124" t="s" s="2">
         <v>19</v>
@@ -16608,7 +16614,7 @@
         <v>19</v>
       </c>
       <c r="AF124" t="s" s="2">
-        <v>644</v>
+        <v>646</v>
       </c>
       <c r="AG124" t="s" s="2">
         <v>76</v>
@@ -16634,10 +16640,10 @@
     </row>
     <row r="125">
       <c r="A125" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
@@ -16660,17 +16666,17 @@
         <v>19</v>
       </c>
       <c r="K125" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N125" s="2"/>
       <c r="O125" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="P125" t="s" s="2">
         <v>19</v>
@@ -16695,13 +16701,13 @@
         <v>19</v>
       </c>
       <c r="X125" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y125" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="Z125" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AA125" t="s" s="2">
         <v>19</v>
@@ -16719,7 +16725,7 @@
         <v>19</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>648</v>
+        <v>650</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>76</v>
@@ -16745,10 +16751,10 @@
     </row>
     <row r="126">
       <c r="A126" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -16771,19 +16777,19 @@
         <v>19</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O126" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="P126" t="s" s="2">
         <v>19</v>
@@ -16808,13 +16814,13 @@
         <v>19</v>
       </c>
       <c r="X126" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>19</v>
@@ -16832,7 +16838,7 @@
         <v>19</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>654</v>
+        <v>656</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>76</v>
@@ -16858,14 +16864,14 @@
     </row>
     <row r="127">
       <c r="A127" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E127" s="2"/>
       <c r="F127" t="s" s="2">
@@ -16884,19 +16890,19 @@
         <v>19</v>
       </c>
       <c r="K127" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O127" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="P127" t="s" s="2">
         <v>19</v>
@@ -16921,13 +16927,13 @@
         <v>19</v>
       </c>
       <c r="X127" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y127" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Z127" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AA127" t="s" s="2">
         <v>19</v>
@@ -16945,7 +16951,7 @@
         <v>19</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>661</v>
+        <v>663</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>76</v>
@@ -16971,14 +16977,14 @@
     </row>
     <row r="128">
       <c r="A128" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E128" s="2"/>
       <c r="F128" t="s" s="2">
@@ -16997,13 +17003,13 @@
         <v>19</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N128" s="2"/>
       <c r="O128" s="2"/>
@@ -17030,11 +17036,11 @@
         <v>19</v>
       </c>
       <c r="X128" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y128" s="2"/>
       <c r="Z128" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AA128" t="s" s="2">
         <v>19</v>
@@ -17052,7 +17058,7 @@
         <v>19</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>669</v>
+        <v>671</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>76</v>
@@ -17078,10 +17084,10 @@
     </row>
     <row r="129">
       <c r="A129" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17104,17 +17110,17 @@
         <v>19</v>
       </c>
       <c r="K129" t="s" s="2">
-        <v>674</v>
+        <v>676</v>
       </c>
       <c r="L129" t="s" s="2">
-        <v>675</v>
+        <v>677</v>
       </c>
       <c r="M129" t="s" s="2">
-        <v>676</v>
+        <v>678</v>
       </c>
       <c r="N129" s="2"/>
       <c r="O129" t="s" s="2">
-        <v>677</v>
+        <v>679</v>
       </c>
       <c r="P129" t="s" s="2">
         <v>19</v>
@@ -17163,7 +17169,7 @@
         <v>19</v>
       </c>
       <c r="AF129" t="s" s="2">
-        <v>673</v>
+        <v>675</v>
       </c>
       <c r="AG129" t="s" s="2">
         <v>76</v>
@@ -17189,10 +17195,10 @@
     </row>
     <row r="130">
       <c r="A130" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17215,19 +17221,19 @@
         <v>19</v>
       </c>
       <c r="K130" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L130" t="s" s="2">
-        <v>679</v>
+        <v>681</v>
       </c>
       <c r="M130" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N130" t="s" s="2">
-        <v>681</v>
+        <v>683</v>
       </c>
       <c r="O130" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="P130" t="s" s="2">
         <v>19</v>
@@ -17252,13 +17258,13 @@
         <v>19</v>
       </c>
       <c r="X130" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y130" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="Z130" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AA130" t="s" s="2">
         <v>19</v>
@@ -17276,7 +17282,7 @@
         <v>19</v>
       </c>
       <c r="AF130" t="s" s="2">
-        <v>678</v>
+        <v>680</v>
       </c>
       <c r="AG130" t="s" s="2">
         <v>76</v>
@@ -17302,10 +17308,10 @@
     </row>
     <row r="131">
       <c r="A131" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
@@ -17328,19 +17334,19 @@
         <v>19</v>
       </c>
       <c r="K131" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N131" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="O131" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="P131" t="s" s="2">
         <v>19</v>
@@ -17365,13 +17371,13 @@
         <v>19</v>
       </c>
       <c r="X131" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y131" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="Z131" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AA131" t="s" s="2">
         <v>19</v>
@@ -17389,7 +17395,7 @@
         <v>19</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>685</v>
+        <v>687</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>76</v>
@@ -17415,10 +17421,10 @@
     </row>
     <row r="132">
       <c r="A132" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -17441,17 +17447,17 @@
         <v>19</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>462</v>
+        <v>464</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>693</v>
+        <v>695</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>694</v>
+        <v>696</v>
       </c>
       <c r="N132" s="2"/>
       <c r="O132" t="s" s="2">
-        <v>695</v>
+        <v>697</v>
       </c>
       <c r="P132" t="s" s="2">
         <v>19</v>
@@ -17500,7 +17506,7 @@
         <v>19</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>692</v>
+        <v>694</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>76</v>
@@ -17518,7 +17524,7 @@
         <v>19</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>239</v>
+        <v>241</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>19</v>
@@ -17526,10 +17532,10 @@
     </row>
     <row r="133">
       <c r="A133" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -17552,17 +17558,17 @@
         <v>19</v>
       </c>
       <c r="K133" t="s" s="2">
-        <v>697</v>
+        <v>699</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>698</v>
+        <v>700</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>699</v>
+        <v>701</v>
       </c>
       <c r="N133" s="2"/>
       <c r="O133" t="s" s="2">
-        <v>700</v>
+        <v>702</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>19</v>
@@ -17587,13 +17593,13 @@
         <v>19</v>
       </c>
       <c r="X133" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y133" t="s" s="2">
-        <v>701</v>
+        <v>703</v>
       </c>
       <c r="Z133" t="s" s="2">
-        <v>702</v>
+        <v>704</v>
       </c>
       <c r="AA133" t="s" s="2">
         <v>19</v>
@@ -17611,7 +17617,7 @@
         <v>19</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>696</v>
+        <v>698</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>76</v>
@@ -17629,7 +17635,7 @@
         <v>19</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>377</v>
+        <v>379</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>19</v>
@@ -17637,10 +17643,10 @@
     </row>
     <row r="134">
       <c r="A134" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="C134" s="2"/>
       <c r="D134" t="s" s="2">
@@ -17663,17 +17669,17 @@
         <v>19</v>
       </c>
       <c r="K134" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L134" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M134" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N134" s="2"/>
       <c r="O134" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="P134" t="s" s="2">
         <v>19</v>
@@ -17722,7 +17728,7 @@
         <v>19</v>
       </c>
       <c r="AF134" t="s" s="2">
-        <v>703</v>
+        <v>705</v>
       </c>
       <c r="AG134" t="s" s="2">
         <v>76</v>
@@ -17748,10 +17754,10 @@
     </row>
     <row r="135">
       <c r="A135" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="C135" s="2"/>
       <c r="D135" t="s" s="2">
@@ -17774,17 +17780,17 @@
         <v>19</v>
       </c>
       <c r="K135" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L135" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M135" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N135" s="2"/>
       <c r="O135" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="P135" t="s" s="2">
         <v>19</v>
@@ -17833,7 +17839,7 @@
         <v>19</v>
       </c>
       <c r="AF135" t="s" s="2">
-        <v>704</v>
+        <v>706</v>
       </c>
       <c r="AG135" t="s" s="2">
         <v>76</v>
@@ -17859,10 +17865,10 @@
     </row>
     <row r="136">
       <c r="A136" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="B136" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="C136" s="2"/>
       <c r="D136" t="s" s="2">
@@ -17885,17 +17891,17 @@
         <v>19</v>
       </c>
       <c r="K136" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L136" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M136" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N136" s="2"/>
       <c r="O136" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="P136" t="s" s="2">
         <v>19</v>
@@ -17944,7 +17950,7 @@
         <v>19</v>
       </c>
       <c r="AF136" t="s" s="2">
-        <v>709</v>
+        <v>711</v>
       </c>
       <c r="AG136" t="s" s="2">
         <v>76</v>
@@ -17970,10 +17976,10 @@
     </row>
     <row r="137">
       <c r="A137" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="C137" s="2"/>
       <c r="D137" t="s" s="2">
@@ -17996,19 +18002,19 @@
         <v>19</v>
       </c>
       <c r="K137" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L137" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M137" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N137" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="O137" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="P137" t="s" s="2">
         <v>19</v>
@@ -18057,7 +18063,7 @@
         <v>19</v>
       </c>
       <c r="AF137" t="s" s="2">
-        <v>713</v>
+        <v>715</v>
       </c>
       <c r="AG137" t="s" s="2">
         <v>76</v>
@@ -18083,10 +18089,10 @@
     </row>
     <row r="138">
       <c r="A138" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="C138" s="2"/>
       <c r="D138" t="s" s="2">
@@ -18109,17 +18115,17 @@
         <v>19</v>
       </c>
       <c r="K138" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L138" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M138" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N138" s="2"/>
       <c r="O138" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P138" t="s" s="2">
         <v>19</v>
@@ -18168,7 +18174,7 @@
         <v>19</v>
       </c>
       <c r="AF138" t="s" s="2">
-        <v>719</v>
+        <v>721</v>
       </c>
       <c r="AG138" t="s" s="2">
         <v>76</v>
@@ -18194,10 +18200,10 @@
     </row>
     <row r="139">
       <c r="A139" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="B139" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="C139" s="2"/>
       <c r="D139" t="s" s="2">
@@ -18220,19 +18226,19 @@
         <v>19</v>
       </c>
       <c r="K139" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L139" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M139" t="s" s="2">
-        <v>725</v>
+        <v>727</v>
       </c>
       <c r="N139" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="O139" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="P139" t="s" s="2">
         <v>19</v>
@@ -18281,7 +18287,7 @@
         <v>19</v>
       </c>
       <c r="AF139" t="s" s="2">
-        <v>723</v>
+        <v>725</v>
       </c>
       <c r="AG139" t="s" s="2">
         <v>76</v>
@@ -18307,10 +18313,10 @@
     </row>
     <row r="140">
       <c r="A140" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="B140" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="C140" s="2"/>
       <c r="D140" t="s" s="2">
@@ -18333,17 +18339,17 @@
         <v>19</v>
       </c>
       <c r="K140" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L140" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M140" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N140" s="2"/>
       <c r="O140" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P140" t="s" s="2">
         <v>19</v>
@@ -18392,7 +18398,7 @@
         <v>19</v>
       </c>
       <c r="AF140" t="s" s="2">
-        <v>728</v>
+        <v>730</v>
       </c>
       <c r="AG140" t="s" s="2">
         <v>76</v>
@@ -18418,10 +18424,10 @@
     </row>
     <row r="141">
       <c r="A141" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="B141" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="C141" s="2"/>
       <c r="D141" t="s" s="2">
@@ -18444,13 +18450,13 @@
         <v>19</v>
       </c>
       <c r="K141" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L141" t="s" s="2">
-        <v>730</v>
+        <v>732</v>
       </c>
       <c r="M141" t="s" s="2">
-        <v>731</v>
+        <v>733</v>
       </c>
       <c r="N141" s="2"/>
       <c r="O141" s="2"/>
@@ -18501,7 +18507,7 @@
         <v>19</v>
       </c>
       <c r="AF141" t="s" s="2">
-        <v>729</v>
+        <v>731</v>
       </c>
       <c r="AG141" t="s" s="2">
         <v>76</v>
@@ -18527,10 +18533,10 @@
     </row>
     <row r="142">
       <c r="A142" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="B142" t="s" s="2">
-        <v>732</v>
+        <v>734</v>
       </c>
       <c r="C142" s="2"/>
       <c r="D142" t="s" s="2">
@@ -18553,13 +18559,13 @@
         <v>19</v>
       </c>
       <c r="K142" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L142" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M142" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N142" s="2"/>
       <c r="O142" s="2"/>
@@ -18610,7 +18616,7 @@
         <v>19</v>
       </c>
       <c r="AF142" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG142" t="s" s="2">
         <v>76</v>
@@ -18619,7 +18625,7 @@
         <v>87</v>
       </c>
       <c r="AI142" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ142" t="s" s="2">
         <v>19</v>
@@ -18631,19 +18637,19 @@
         <v>19</v>
       </c>
       <c r="AM142" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="B143" t="s" s="2">
-        <v>733</v>
+        <v>735</v>
       </c>
       <c r="C143" s="2"/>
       <c r="D143" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E143" s="2"/>
       <c r="F143" t="s" s="2">
@@ -18665,13 +18671,13 @@
         <v>134</v>
       </c>
       <c r="L143" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M143" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N143" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O143" s="2"/>
       <c r="P143" t="s" s="2">
@@ -18721,7 +18727,7 @@
         <v>19</v>
       </c>
       <c r="AF143" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG143" t="s" s="2">
         <v>76</v>
@@ -18742,19 +18748,19 @@
         <v>19</v>
       </c>
       <c r="AM143" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="B144" t="s" s="2">
-        <v>734</v>
+        <v>736</v>
       </c>
       <c r="C144" s="2"/>
       <c r="D144" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E144" s="2"/>
       <c r="F144" t="s" s="2">
@@ -18776,16 +18782,16 @@
         <v>134</v>
       </c>
       <c r="L144" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M144" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N144" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O144" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P144" t="s" s="2">
         <v>19</v>
@@ -18834,7 +18840,7 @@
         <v>19</v>
       </c>
       <c r="AF144" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG144" t="s" s="2">
         <v>76</v>
@@ -18860,10 +18866,10 @@
     </row>
     <row r="145">
       <c r="A145" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="C145" s="2"/>
       <c r="D145" t="s" s="2">
@@ -18886,19 +18892,19 @@
         <v>19</v>
       </c>
       <c r="K145" t="s" s="2">
-        <v>736</v>
+        <v>738</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>737</v>
+        <v>739</v>
       </c>
       <c r="M145" t="s" s="2">
-        <v>738</v>
+        <v>740</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>739</v>
+        <v>741</v>
       </c>
       <c r="O145" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="P145" t="s" s="2">
         <v>19</v>
@@ -18923,11 +18929,11 @@
         <v>19</v>
       </c>
       <c r="X145" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y145" s="2"/>
       <c r="Z145" t="s" s="2">
-        <v>741</v>
+        <v>743</v>
       </c>
       <c r="AA145" t="s" s="2">
         <v>19</v>
@@ -18945,7 +18951,7 @@
         <v>19</v>
       </c>
       <c r="AF145" t="s" s="2">
-        <v>735</v>
+        <v>737</v>
       </c>
       <c r="AG145" t="s" s="2">
         <v>87</v>
@@ -18971,10 +18977,10 @@
     </row>
     <row r="146">
       <c r="A146" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="C146" s="2"/>
       <c r="D146" t="s" s="2">
@@ -18997,17 +19003,17 @@
         <v>19</v>
       </c>
       <c r="K146" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L146" t="s" s="2">
-        <v>743</v>
+        <v>745</v>
       </c>
       <c r="M146" t="s" s="2">
-        <v>744</v>
+        <v>746</v>
       </c>
       <c r="N146" s="2"/>
       <c r="O146" t="s" s="2">
-        <v>740</v>
+        <v>742</v>
       </c>
       <c r="P146" t="s" s="2">
         <v>19</v>
@@ -19032,11 +19038,11 @@
         <v>19</v>
       </c>
       <c r="X146" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y146" s="2"/>
       <c r="Z146" t="s" s="2">
-        <v>745</v>
+        <v>747</v>
       </c>
       <c r="AA146" t="s" s="2">
         <v>19</v>
@@ -19054,7 +19060,7 @@
         <v>19</v>
       </c>
       <c r="AF146" t="s" s="2">
-        <v>742</v>
+        <v>744</v>
       </c>
       <c r="AG146" t="s" s="2">
         <v>76</v>
@@ -19080,10 +19086,10 @@
     </row>
     <row r="147">
       <c r="A147" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="C147" s="2"/>
       <c r="D147" t="s" s="2">
@@ -19106,19 +19112,19 @@
         <v>19</v>
       </c>
       <c r="K147" t="s" s="2">
-        <v>359</v>
+        <v>361</v>
       </c>
       <c r="L147" t="s" s="2">
-        <v>360</v>
+        <v>362</v>
       </c>
       <c r="M147" t="s" s="2">
-        <v>361</v>
+        <v>363</v>
       </c>
       <c r="N147" t="s" s="2">
-        <v>362</v>
+        <v>364</v>
       </c>
       <c r="O147" t="s" s="2">
-        <v>363</v>
+        <v>365</v>
       </c>
       <c r="P147" t="s" s="2">
         <v>19</v>
@@ -19167,7 +19173,7 @@
         <v>19</v>
       </c>
       <c r="AF147" t="s" s="2">
-        <v>746</v>
+        <v>748</v>
       </c>
       <c r="AG147" t="s" s="2">
         <v>76</v>
@@ -19182,7 +19188,7 @@
         <v>99</v>
       </c>
       <c r="AK147" t="s" s="2">
-        <v>747</v>
+        <v>749</v>
       </c>
       <c r="AL147" t="s" s="2">
         <v>19</v>
@@ -19193,10 +19199,10 @@
     </row>
     <row r="148">
       <c r="A148" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="C148" s="2"/>
       <c r="D148" t="s" s="2">
@@ -19219,17 +19225,17 @@
         <v>19</v>
       </c>
       <c r="K148" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L148" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M148" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="N148" s="2"/>
       <c r="O148" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="P148" t="s" s="2">
         <v>19</v>
@@ -19278,7 +19284,7 @@
         <v>19</v>
       </c>
       <c r="AF148" t="s" s="2">
-        <v>748</v>
+        <v>750</v>
       </c>
       <c r="AG148" t="s" s="2">
         <v>76</v>
@@ -19304,10 +19310,10 @@
     </row>
     <row r="149">
       <c r="A149" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>750</v>
+        <v>752</v>
       </c>
       <c r="C149" s="2"/>
       <c r="D149" t="s" s="2">
@@ -19330,13 +19336,13 @@
         <v>19</v>
       </c>
       <c r="K149" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L149" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M149" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N149" s="2"/>
       <c r="O149" s="2"/>
@@ -19387,7 +19393,7 @@
         <v>19</v>
       </c>
       <c r="AF149" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG149" t="s" s="2">
         <v>76</v>
@@ -19396,7 +19402,7 @@
         <v>87</v>
       </c>
       <c r="AI149" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ149" t="s" s="2">
         <v>19</v>
@@ -19408,19 +19414,19 @@
         <v>19</v>
       </c>
       <c r="AM149" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>751</v>
+        <v>753</v>
       </c>
       <c r="C150" s="2"/>
       <c r="D150" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E150" s="2"/>
       <c r="F150" t="s" s="2">
@@ -19442,13 +19448,13 @@
         <v>134</v>
       </c>
       <c r="L150" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M150" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N150" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" t="s" s="2">
@@ -19498,7 +19504,7 @@
         <v>19</v>
       </c>
       <c r="AF150" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG150" t="s" s="2">
         <v>76</v>
@@ -19519,19 +19525,19 @@
         <v>19</v>
       </c>
       <c r="AM150" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>752</v>
+        <v>754</v>
       </c>
       <c r="C151" s="2"/>
       <c r="D151" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E151" s="2"/>
       <c r="F151" t="s" s="2">
@@ -19553,16 +19559,16 @@
         <v>134</v>
       </c>
       <c r="L151" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M151" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N151" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O151" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P151" t="s" s="2">
         <v>19</v>
@@ -19611,7 +19617,7 @@
         <v>19</v>
       </c>
       <c r="AF151" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG151" t="s" s="2">
         <v>76</v>
@@ -19637,10 +19643,10 @@
     </row>
     <row r="152">
       <c r="A152" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="C152" s="2"/>
       <c r="D152" t="s" s="2">
@@ -19663,17 +19669,17 @@
         <v>19</v>
       </c>
       <c r="K152" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L152" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N152" s="2"/>
       <c r="O152" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P152" t="s" s="2">
         <v>19</v>
@@ -19722,7 +19728,7 @@
         <v>19</v>
       </c>
       <c r="AF152" t="s" s="2">
-        <v>753</v>
+        <v>755</v>
       </c>
       <c r="AG152" t="s" s="2">
         <v>87</v>
@@ -19748,10 +19754,10 @@
     </row>
     <row r="153">
       <c r="A153" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="C153" s="2"/>
       <c r="D153" t="s" s="2">
@@ -19774,17 +19780,17 @@
         <v>19</v>
       </c>
       <c r="K153" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L153" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M153" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N153" s="2"/>
       <c r="O153" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P153" t="s" s="2">
         <v>19</v>
@@ -19833,7 +19839,7 @@
         <v>19</v>
       </c>
       <c r="AF153" t="s" s="2">
-        <v>754</v>
+        <v>756</v>
       </c>
       <c r="AG153" t="s" s="2">
         <v>76</v>
@@ -19859,10 +19865,10 @@
     </row>
     <row r="154">
       <c r="A154" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="C154" s="2"/>
       <c r="D154" t="s" s="2">
@@ -19885,17 +19891,17 @@
         <v>19</v>
       </c>
       <c r="K154" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L154" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M154" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N154" s="2"/>
       <c r="O154" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="P154" t="s" s="2">
         <v>19</v>
@@ -19920,13 +19926,13 @@
         <v>19</v>
       </c>
       <c r="X154" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y154" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="Z154" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AA154" t="s" s="2">
         <v>19</v>
@@ -19944,7 +19950,7 @@
         <v>19</v>
       </c>
       <c r="AF154" t="s" s="2">
-        <v>755</v>
+        <v>757</v>
       </c>
       <c r="AG154" t="s" s="2">
         <v>76</v>
@@ -19970,10 +19976,10 @@
     </row>
     <row r="155">
       <c r="A155" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="C155" s="2"/>
       <c r="D155" t="s" s="2">
@@ -19996,19 +20002,19 @@
         <v>19</v>
       </c>
       <c r="K155" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L155" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M155" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N155" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O155" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="P155" t="s" s="2">
         <v>19</v>
@@ -20033,13 +20039,13 @@
         <v>19</v>
       </c>
       <c r="X155" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y155" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="Z155" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AA155" t="s" s="2">
         <v>19</v>
@@ -20057,7 +20063,7 @@
         <v>19</v>
       </c>
       <c r="AF155" t="s" s="2">
-        <v>756</v>
+        <v>758</v>
       </c>
       <c r="AG155" t="s" s="2">
         <v>76</v>
@@ -20083,14 +20089,14 @@
     </row>
     <row r="156">
       <c r="A156" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="C156" s="2"/>
       <c r="D156" t="s" s="2">
-        <v>662</v>
+        <v>664</v>
       </c>
       <c r="E156" s="2"/>
       <c r="F156" t="s" s="2">
@@ -20109,19 +20115,19 @@
         <v>19</v>
       </c>
       <c r="K156" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L156" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M156" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N156" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O156" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="P156" t="s" s="2">
         <v>19</v>
@@ -20146,13 +20152,13 @@
         <v>19</v>
       </c>
       <c r="X156" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y156" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Z156" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AA156" t="s" s="2">
         <v>19</v>
@@ -20170,7 +20176,7 @@
         <v>19</v>
       </c>
       <c r="AF156" t="s" s="2">
-        <v>757</v>
+        <v>759</v>
       </c>
       <c r="AG156" t="s" s="2">
         <v>76</v>
@@ -20196,14 +20202,14 @@
     </row>
     <row r="157">
       <c r="A157" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="C157" s="2"/>
       <c r="D157" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E157" s="2"/>
       <c r="F157" t="s" s="2">
@@ -20222,13 +20228,13 @@
         <v>19</v>
       </c>
       <c r="K157" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L157" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M157" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N157" s="2"/>
       <c r="O157" s="2"/>
@@ -20255,11 +20261,11 @@
         <v>19</v>
       </c>
       <c r="X157" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y157" s="2"/>
       <c r="Z157" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AA157" t="s" s="2">
         <v>19</v>
@@ -20277,7 +20283,7 @@
         <v>19</v>
       </c>
       <c r="AF157" t="s" s="2">
-        <v>758</v>
+        <v>760</v>
       </c>
       <c r="AG157" t="s" s="2">
         <v>76</v>
@@ -20303,10 +20309,10 @@
     </row>
     <row r="158">
       <c r="A158" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="C158" s="2"/>
       <c r="D158" t="s" s="2">
@@ -20329,19 +20335,19 @@
         <v>19</v>
       </c>
       <c r="K158" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L158" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="M158" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N158" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="O158" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="P158" t="s" s="2">
         <v>19</v>
@@ -20366,13 +20372,13 @@
         <v>19</v>
       </c>
       <c r="X158" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y158" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="Z158" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AA158" t="s" s="2">
         <v>19</v>
@@ -20390,7 +20396,7 @@
         <v>19</v>
       </c>
       <c r="AF158" t="s" s="2">
-        <v>759</v>
+        <v>761</v>
       </c>
       <c r="AG158" t="s" s="2">
         <v>76</v>
@@ -20416,10 +20422,10 @@
     </row>
     <row r="159">
       <c r="A159" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="C159" s="2"/>
       <c r="D159" t="s" s="2">
@@ -20442,19 +20448,19 @@
         <v>19</v>
       </c>
       <c r="K159" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L159" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M159" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N159" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="O159" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="P159" t="s" s="2">
         <v>19</v>
@@ -20479,13 +20485,13 @@
         <v>19</v>
       </c>
       <c r="X159" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y159" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="Z159" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AA159" t="s" s="2">
         <v>19</v>
@@ -20503,7 +20509,7 @@
         <v>19</v>
       </c>
       <c r="AF159" t="s" s="2">
-        <v>762</v>
+        <v>764</v>
       </c>
       <c r="AG159" t="s" s="2">
         <v>76</v>
@@ -20529,10 +20535,10 @@
     </row>
     <row r="160">
       <c r="A160" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="C160" s="2"/>
       <c r="D160" t="s" s="2">
@@ -20555,17 +20561,17 @@
         <v>19</v>
       </c>
       <c r="K160" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L160" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M160" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N160" s="2"/>
       <c r="O160" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="P160" t="s" s="2">
         <v>19</v>
@@ -20614,7 +20620,7 @@
         <v>19</v>
       </c>
       <c r="AF160" t="s" s="2">
-        <v>763</v>
+        <v>765</v>
       </c>
       <c r="AG160" t="s" s="2">
         <v>76</v>
@@ -20640,10 +20646,10 @@
     </row>
     <row r="161">
       <c r="A161" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="C161" s="2"/>
       <c r="D161" t="s" s="2">
@@ -20666,17 +20672,17 @@
         <v>19</v>
       </c>
       <c r="K161" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L161" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M161" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N161" s="2"/>
       <c r="O161" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="P161" t="s" s="2">
         <v>19</v>
@@ -20725,7 +20731,7 @@
         <v>19</v>
       </c>
       <c r="AF161" t="s" s="2">
-        <v>764</v>
+        <v>766</v>
       </c>
       <c r="AG161" t="s" s="2">
         <v>76</v>
@@ -20751,10 +20757,10 @@
     </row>
     <row r="162">
       <c r="A162" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="C162" s="2"/>
       <c r="D162" t="s" s="2">
@@ -20777,17 +20783,17 @@
         <v>19</v>
       </c>
       <c r="K162" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L162" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M162" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N162" s="2"/>
       <c r="O162" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="P162" t="s" s="2">
         <v>19</v>
@@ -20836,7 +20842,7 @@
         <v>19</v>
       </c>
       <c r="AF162" t="s" s="2">
-        <v>765</v>
+        <v>767</v>
       </c>
       <c r="AG162" t="s" s="2">
         <v>76</v>
@@ -20862,10 +20868,10 @@
     </row>
     <row r="163">
       <c r="A163" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="C163" s="2"/>
       <c r="D163" t="s" s="2">
@@ -20888,19 +20894,19 @@
         <v>19</v>
       </c>
       <c r="K163" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M163" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N163" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="O163" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="P163" t="s" s="2">
         <v>19</v>
@@ -20949,7 +20955,7 @@
         <v>19</v>
       </c>
       <c r="AF163" t="s" s="2">
-        <v>766</v>
+        <v>768</v>
       </c>
       <c r="AG163" t="s" s="2">
         <v>76</v>
@@ -20975,10 +20981,10 @@
     </row>
     <row r="164">
       <c r="A164" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="C164" s="2"/>
       <c r="D164" t="s" s="2">
@@ -21001,17 +21007,17 @@
         <v>19</v>
       </c>
       <c r="K164" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L164" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M164" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N164" s="2"/>
       <c r="O164" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P164" t="s" s="2">
         <v>19</v>
@@ -21060,7 +21066,7 @@
         <v>19</v>
       </c>
       <c r="AF164" t="s" s="2">
-        <v>767</v>
+        <v>769</v>
       </c>
       <c r="AG164" t="s" s="2">
         <v>76</v>
@@ -21086,10 +21092,10 @@
     </row>
     <row r="165">
       <c r="A165" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="C165" s="2"/>
       <c r="D165" t="s" s="2">
@@ -21112,19 +21118,19 @@
         <v>19</v>
       </c>
       <c r="K165" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L165" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M165" t="s" s="2">
-        <v>769</v>
+        <v>771</v>
       </c>
       <c r="N165" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="O165" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="P165" t="s" s="2">
         <v>19</v>
@@ -21173,7 +21179,7 @@
         <v>19</v>
       </c>
       <c r="AF165" t="s" s="2">
-        <v>768</v>
+        <v>770</v>
       </c>
       <c r="AG165" t="s" s="2">
         <v>76</v>
@@ -21199,10 +21205,10 @@
     </row>
     <row r="166">
       <c r="A166" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="C166" s="2"/>
       <c r="D166" t="s" s="2">
@@ -21225,17 +21231,17 @@
         <v>19</v>
       </c>
       <c r="K166" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L166" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M166" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N166" s="2"/>
       <c r="O166" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P166" t="s" s="2">
         <v>19</v>
@@ -21284,7 +21290,7 @@
         <v>19</v>
       </c>
       <c r="AF166" t="s" s="2">
-        <v>770</v>
+        <v>772</v>
       </c>
       <c r="AG166" t="s" s="2">
         <v>76</v>
@@ -21310,10 +21316,10 @@
     </row>
     <row r="167">
       <c r="A167" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="C167" s="2"/>
       <c r="D167" t="s" s="2">
@@ -21336,17 +21342,17 @@
         <v>19</v>
       </c>
       <c r="K167" t="s" s="2">
-        <v>282</v>
+        <v>284</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>621</v>
+        <v>623</v>
       </c>
       <c r="M167" t="s" s="2">
-        <v>749</v>
+        <v>751</v>
       </c>
       <c r="N167" s="2"/>
       <c r="O167" t="s" s="2">
-        <v>623</v>
+        <v>625</v>
       </c>
       <c r="P167" t="s" s="2">
         <v>19</v>
@@ -21395,7 +21401,7 @@
         <v>19</v>
       </c>
       <c r="AF167" t="s" s="2">
-        <v>771</v>
+        <v>773</v>
       </c>
       <c r="AG167" t="s" s="2">
         <v>76</v>
@@ -21421,10 +21427,10 @@
     </row>
     <row r="168">
       <c r="A168" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>772</v>
+        <v>774</v>
       </c>
       <c r="C168" s="2"/>
       <c r="D168" t="s" s="2">
@@ -21447,13 +21453,13 @@
         <v>19</v>
       </c>
       <c r="K168" t="s" s="2">
-        <v>288</v>
+        <v>290</v>
       </c>
       <c r="L168" t="s" s="2">
-        <v>289</v>
+        <v>291</v>
       </c>
       <c r="M168" t="s" s="2">
-        <v>290</v>
+        <v>292</v>
       </c>
       <c r="N168" s="2"/>
       <c r="O168" s="2"/>
@@ -21504,7 +21510,7 @@
         <v>19</v>
       </c>
       <c r="AF168" t="s" s="2">
-        <v>291</v>
+        <v>293</v>
       </c>
       <c r="AG168" t="s" s="2">
         <v>76</v>
@@ -21513,7 +21519,7 @@
         <v>87</v>
       </c>
       <c r="AI168" t="s" s="2">
-        <v>292</v>
+        <v>294</v>
       </c>
       <c r="AJ168" t="s" s="2">
         <v>19</v>
@@ -21525,19 +21531,19 @@
         <v>19</v>
       </c>
       <c r="AM168" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>773</v>
+        <v>775</v>
       </c>
       <c r="C169" s="2"/>
       <c r="D169" t="s" s="2">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="E169" s="2"/>
       <c r="F169" t="s" s="2">
@@ -21559,13 +21565,13 @@
         <v>134</v>
       </c>
       <c r="L169" t="s" s="2">
-        <v>295</v>
+        <v>297</v>
       </c>
       <c r="M169" t="s" s="2">
-        <v>296</v>
+        <v>298</v>
       </c>
       <c r="N169" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" t="s" s="2">
@@ -21615,7 +21621,7 @@
         <v>19</v>
       </c>
       <c r="AF169" t="s" s="2">
-        <v>297</v>
+        <v>299</v>
       </c>
       <c r="AG169" t="s" s="2">
         <v>76</v>
@@ -21636,19 +21642,19 @@
         <v>19</v>
       </c>
       <c r="AM169" t="s" s="2">
-        <v>293</v>
+        <v>295</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>774</v>
+        <v>776</v>
       </c>
       <c r="C170" s="2"/>
       <c r="D170" t="s" s="2">
-        <v>299</v>
+        <v>301</v>
       </c>
       <c r="E170" s="2"/>
       <c r="F170" t="s" s="2">
@@ -21670,16 +21676,16 @@
         <v>134</v>
       </c>
       <c r="L170" t="s" s="2">
-        <v>300</v>
+        <v>302</v>
       </c>
       <c r="M170" t="s" s="2">
-        <v>301</v>
+        <v>303</v>
       </c>
       <c r="N170" t="s" s="2">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O170" t="s" s="2">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="P170" t="s" s="2">
         <v>19</v>
@@ -21728,7 +21734,7 @@
         <v>19</v>
       </c>
       <c r="AF170" t="s" s="2">
-        <v>302</v>
+        <v>304</v>
       </c>
       <c r="AG170" t="s" s="2">
         <v>76</v>
@@ -21754,10 +21760,10 @@
     </row>
     <row r="171">
       <c r="A171" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="C171" s="2"/>
       <c r="D171" t="s" s="2">
@@ -21780,17 +21786,17 @@
         <v>19</v>
       </c>
       <c r="K171" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="L171" t="s" s="2">
-        <v>628</v>
+        <v>630</v>
       </c>
       <c r="M171" t="s" s="2">
-        <v>629</v>
+        <v>631</v>
       </c>
       <c r="N171" s="2"/>
       <c r="O171" t="s" s="2">
-        <v>630</v>
+        <v>632</v>
       </c>
       <c r="P171" t="s" s="2">
         <v>19</v>
@@ -21839,7 +21845,7 @@
         <v>19</v>
       </c>
       <c r="AF171" t="s" s="2">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="AG171" t="s" s="2">
         <v>87</v>
@@ -21865,10 +21871,10 @@
     </row>
     <row r="172">
       <c r="A172" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="C172" s="2"/>
       <c r="D172" t="s" s="2">
@@ -21891,17 +21897,17 @@
         <v>19</v>
       </c>
       <c r="K172" t="s" s="2">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="L172" t="s" s="2">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="M172" t="s" s="2">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="N172" s="2"/>
       <c r="O172" t="s" s="2">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="P172" t="s" s="2">
         <v>19</v>
@@ -21950,7 +21956,7 @@
         <v>19</v>
       </c>
       <c r="AF172" t="s" s="2">
-        <v>776</v>
+        <v>778</v>
       </c>
       <c r="AG172" t="s" s="2">
         <v>76</v>
@@ -21976,10 +21982,10 @@
     </row>
     <row r="173">
       <c r="A173" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="C173" s="2"/>
       <c r="D173" t="s" s="2">
@@ -22002,17 +22008,17 @@
         <v>19</v>
       </c>
       <c r="K173" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L173" t="s" s="2">
-        <v>649</v>
+        <v>651</v>
       </c>
       <c r="M173" t="s" s="2">
-        <v>650</v>
+        <v>652</v>
       </c>
       <c r="N173" s="2"/>
       <c r="O173" t="s" s="2">
-        <v>651</v>
+        <v>653</v>
       </c>
       <c r="P173" t="s" s="2">
         <v>19</v>
@@ -22037,13 +22043,13 @@
         <v>19</v>
       </c>
       <c r="X173" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y173" t="s" s="2">
-        <v>652</v>
+        <v>654</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>653</v>
+        <v>655</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>19</v>
@@ -22061,7 +22067,7 @@
         <v>19</v>
       </c>
       <c r="AF173" t="s" s="2">
-        <v>777</v>
+        <v>779</v>
       </c>
       <c r="AG173" t="s" s="2">
         <v>76</v>
@@ -22087,10 +22093,10 @@
     </row>
     <row r="174">
       <c r="A174" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="C174" s="2"/>
       <c r="D174" t="s" s="2">
@@ -22113,19 +22119,19 @@
         <v>19</v>
       </c>
       <c r="K174" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L174" t="s" s="2">
-        <v>655</v>
+        <v>657</v>
       </c>
       <c r="M174" t="s" s="2">
-        <v>656</v>
+        <v>658</v>
       </c>
       <c r="N174" t="s" s="2">
-        <v>657</v>
+        <v>659</v>
       </c>
       <c r="O174" t="s" s="2">
-        <v>658</v>
+        <v>660</v>
       </c>
       <c r="P174" t="s" s="2">
         <v>19</v>
@@ -22150,13 +22156,13 @@
         <v>19</v>
       </c>
       <c r="X174" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y174" t="s" s="2">
-        <v>659</v>
+        <v>661</v>
       </c>
       <c r="Z174" t="s" s="2">
-        <v>660</v>
+        <v>662</v>
       </c>
       <c r="AA174" t="s" s="2">
         <v>19</v>
@@ -22174,7 +22180,7 @@
         <v>19</v>
       </c>
       <c r="AF174" t="s" s="2">
-        <v>778</v>
+        <v>780</v>
       </c>
       <c r="AG174" t="s" s="2">
         <v>76</v>
@@ -22200,10 +22206,10 @@
     </row>
     <row r="175">
       <c r="A175" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="C175" s="2"/>
       <c r="D175" t="s" s="2">
@@ -22226,19 +22232,19 @@
         <v>19</v>
       </c>
       <c r="K175" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L175" t="s" s="2">
-        <v>663</v>
+        <v>665</v>
       </c>
       <c r="M175" t="s" s="2">
-        <v>664</v>
+        <v>666</v>
       </c>
       <c r="N175" t="s" s="2">
-        <v>665</v>
+        <v>667</v>
       </c>
       <c r="O175" t="s" s="2">
-        <v>666</v>
+        <v>668</v>
       </c>
       <c r="P175" t="s" s="2">
         <v>19</v>
@@ -22263,13 +22269,13 @@
         <v>19</v>
       </c>
       <c r="X175" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y175" t="s" s="2">
-        <v>667</v>
+        <v>669</v>
       </c>
       <c r="Z175" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AA175" t="s" s="2">
         <v>19</v>
@@ -22287,7 +22293,7 @@
         <v>19</v>
       </c>
       <c r="AF175" t="s" s="2">
-        <v>779</v>
+        <v>781</v>
       </c>
       <c r="AG175" t="s" s="2">
         <v>76</v>
@@ -22313,14 +22319,14 @@
     </row>
     <row r="176">
       <c r="A176" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="C176" s="2"/>
       <c r="D176" t="s" s="2">
-        <v>670</v>
+        <v>672</v>
       </c>
       <c r="E176" s="2"/>
       <c r="F176" t="s" s="2">
@@ -22339,13 +22345,13 @@
         <v>19</v>
       </c>
       <c r="K176" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L176" t="s" s="2">
-        <v>671</v>
+        <v>673</v>
       </c>
       <c r="M176" t="s" s="2">
-        <v>672</v>
+        <v>674</v>
       </c>
       <c r="N176" s="2"/>
       <c r="O176" s="2"/>
@@ -22372,11 +22378,11 @@
         <v>19</v>
       </c>
       <c r="X176" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y176" s="2"/>
       <c r="Z176" t="s" s="2">
-        <v>668</v>
+        <v>670</v>
       </c>
       <c r="AA176" t="s" s="2">
         <v>19</v>
@@ -22394,7 +22400,7 @@
         <v>19</v>
       </c>
       <c r="AF176" t="s" s="2">
-        <v>780</v>
+        <v>782</v>
       </c>
       <c r="AG176" t="s" s="2">
         <v>76</v>
@@ -22420,10 +22426,10 @@
     </row>
     <row r="177">
       <c r="A177" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="C177" s="2"/>
       <c r="D177" t="s" s="2">
@@ -22446,19 +22452,19 @@
         <v>19</v>
       </c>
       <c r="K177" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L177" t="s" s="2">
-        <v>760</v>
+        <v>762</v>
       </c>
       <c r="M177" t="s" s="2">
-        <v>680</v>
+        <v>682</v>
       </c>
       <c r="N177" t="s" s="2">
-        <v>761</v>
+        <v>763</v>
       </c>
       <c r="O177" t="s" s="2">
-        <v>682</v>
+        <v>684</v>
       </c>
       <c r="P177" t="s" s="2">
         <v>19</v>
@@ -22483,13 +22489,13 @@
         <v>19</v>
       </c>
       <c r="X177" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y177" t="s" s="2">
-        <v>683</v>
+        <v>685</v>
       </c>
       <c r="Z177" t="s" s="2">
-        <v>684</v>
+        <v>686</v>
       </c>
       <c r="AA177" t="s" s="2">
         <v>19</v>
@@ -22507,7 +22513,7 @@
         <v>19</v>
       </c>
       <c r="AF177" t="s" s="2">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="AG177" t="s" s="2">
         <v>76</v>
@@ -22533,10 +22539,10 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="C178" s="2"/>
       <c r="D178" t="s" s="2">
@@ -22559,19 +22565,19 @@
         <v>19</v>
       </c>
       <c r="K178" t="s" s="2">
-        <v>203</v>
+        <v>205</v>
       </c>
       <c r="L178" t="s" s="2">
-        <v>686</v>
+        <v>688</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>687</v>
+        <v>689</v>
       </c>
       <c r="N178" t="s" s="2">
-        <v>688</v>
+        <v>690</v>
       </c>
       <c r="O178" t="s" s="2">
-        <v>689</v>
+        <v>691</v>
       </c>
       <c r="P178" t="s" s="2">
         <v>19</v>
@@ -22596,13 +22602,13 @@
         <v>19</v>
       </c>
       <c r="X178" t="s" s="2">
-        <v>217</v>
+        <v>219</v>
       </c>
       <c r="Y178" t="s" s="2">
-        <v>690</v>
+        <v>692</v>
       </c>
       <c r="Z178" t="s" s="2">
-        <v>691</v>
+        <v>693</v>
       </c>
       <c r="AA178" t="s" s="2">
         <v>19</v>
@@ -22620,7 +22626,7 @@
         <v>19</v>
       </c>
       <c r="AF178" t="s" s="2">
-        <v>782</v>
+        <v>784</v>
       </c>
       <c r="AG178" t="s" s="2">
         <v>76</v>
@@ -22646,10 +22652,10 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="C179" s="2"/>
       <c r="D179" t="s" s="2">
@@ -22672,17 +22678,17 @@
         <v>19</v>
       </c>
       <c r="K179" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L179" t="s" s="2">
-        <v>617</v>
+        <v>619</v>
       </c>
       <c r="M179" t="s" s="2">
-        <v>618</v>
+        <v>620</v>
       </c>
       <c r="N179" s="2"/>
       <c r="O179" t="s" s="2">
-        <v>619</v>
+        <v>621</v>
       </c>
       <c r="P179" t="s" s="2">
         <v>19</v>
@@ -22731,7 +22737,7 @@
         <v>19</v>
       </c>
       <c r="AF179" t="s" s="2">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="AG179" t="s" s="2">
         <v>76</v>
@@ -22757,10 +22763,10 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="B180" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="C180" s="2"/>
       <c r="D180" t="s" s="2">
@@ -22783,17 +22789,17 @@
         <v>19</v>
       </c>
       <c r="K180" t="s" s="2">
-        <v>705</v>
+        <v>707</v>
       </c>
       <c r="L180" t="s" s="2">
-        <v>706</v>
+        <v>708</v>
       </c>
       <c r="M180" t="s" s="2">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="N180" s="2"/>
       <c r="O180" t="s" s="2">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="P180" t="s" s="2">
         <v>19</v>
@@ -22842,7 +22848,7 @@
         <v>19</v>
       </c>
       <c r="AF180" t="s" s="2">
-        <v>784</v>
+        <v>786</v>
       </c>
       <c r="AG180" t="s" s="2">
         <v>76</v>
@@ -22868,10 +22874,10 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="C181" s="2"/>
       <c r="D181" t="s" s="2">
@@ -22894,17 +22900,17 @@
         <v>19</v>
       </c>
       <c r="K181" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L181" t="s" s="2">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="M181" t="s" s="2">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="N181" s="2"/>
       <c r="O181" t="s" s="2">
-        <v>712</v>
+        <v>714</v>
       </c>
       <c r="P181" t="s" s="2">
         <v>19</v>
@@ -22953,7 +22959,7 @@
         <v>19</v>
       </c>
       <c r="AF181" t="s" s="2">
-        <v>785</v>
+        <v>787</v>
       </c>
       <c r="AG181" t="s" s="2">
         <v>76</v>
@@ -22979,10 +22985,10 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="C182" s="2"/>
       <c r="D182" t="s" s="2">
@@ -23005,19 +23011,19 @@
         <v>19</v>
       </c>
       <c r="K182" t="s" s="2">
-        <v>714</v>
+        <v>716</v>
       </c>
       <c r="L182" t="s" s="2">
-        <v>715</v>
+        <v>717</v>
       </c>
       <c r="M182" t="s" s="2">
-        <v>716</v>
+        <v>718</v>
       </c>
       <c r="N182" t="s" s="2">
-        <v>717</v>
+        <v>719</v>
       </c>
       <c r="O182" t="s" s="2">
-        <v>718</v>
+        <v>720</v>
       </c>
       <c r="P182" t="s" s="2">
         <v>19</v>
@@ -23066,7 +23072,7 @@
         <v>19</v>
       </c>
       <c r="AF182" t="s" s="2">
-        <v>786</v>
+        <v>788</v>
       </c>
       <c r="AG182" t="s" s="2">
         <v>76</v>
@@ -23092,10 +23098,10 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="B183" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="C183" s="2"/>
       <c r="D183" t="s" s="2">
@@ -23118,17 +23124,17 @@
         <v>19</v>
       </c>
       <c r="K183" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L183" t="s" s="2">
-        <v>720</v>
+        <v>722</v>
       </c>
       <c r="M183" t="s" s="2">
-        <v>721</v>
+        <v>723</v>
       </c>
       <c r="N183" s="2"/>
       <c r="O183" t="s" s="2">
-        <v>722</v>
+        <v>724</v>
       </c>
       <c r="P183" t="s" s="2">
         <v>19</v>
@@ -23177,7 +23183,7 @@
         <v>19</v>
       </c>
       <c r="AF183" t="s" s="2">
-        <v>787</v>
+        <v>789</v>
       </c>
       <c r="AG183" t="s" s="2">
         <v>76</v>
@@ -23203,10 +23209,10 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="B184" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="C184" s="2"/>
       <c r="D184" t="s" s="2">
@@ -23229,19 +23235,19 @@
         <v>19</v>
       </c>
       <c r="K184" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L184" t="s" s="2">
-        <v>724</v>
+        <v>726</v>
       </c>
       <c r="M184" t="s" s="2">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="N184" t="s" s="2">
-        <v>726</v>
+        <v>728</v>
       </c>
       <c r="O184" t="s" s="2">
-        <v>727</v>
+        <v>729</v>
       </c>
       <c r="P184" t="s" s="2">
         <v>19</v>
@@ -23290,7 +23296,7 @@
         <v>19</v>
       </c>
       <c r="AF184" t="s" s="2">
-        <v>788</v>
+        <v>790</v>
       </c>
       <c r="AG184" t="s" s="2">
         <v>76</v>
@@ -23316,10 +23322,10 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="B185" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="C185" s="2"/>
       <c r="D185" t="s" s="2">
@@ -23342,17 +23348,17 @@
         <v>19</v>
       </c>
       <c r="K185" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="L185" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="M185" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="N185" s="2"/>
       <c r="O185" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="P185" t="s" s="2">
         <v>19</v>
@@ -23401,7 +23407,7 @@
         <v>19</v>
       </c>
       <c r="AF185" t="s" s="2">
-        <v>790</v>
+        <v>792</v>
       </c>
       <c r="AG185" t="s" s="2">
         <v>76</v>
@@ -23427,10 +23433,10 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="B186" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="C186" s="2"/>
       <c r="D186" t="s" s="2">
@@ -23453,17 +23459,17 @@
         <v>19</v>
       </c>
       <c r="K186" t="s" s="2">
-        <v>616</v>
+        <v>618</v>
       </c>
       <c r="L186" t="s" s="2">
-        <v>792</v>
+        <v>794</v>
       </c>
       <c r="M186" t="s" s="2">
-        <v>793</v>
+        <v>795</v>
       </c>
       <c r="N186" s="2"/>
       <c r="O186" t="s" s="2">
-        <v>794</v>
+        <v>796</v>
       </c>
       <c r="P186" t="s" s="2">
         <v>19</v>
@@ -23512,7 +23518,7 @@
         <v>19</v>
       </c>
       <c r="AF186" t="s" s="2">
-        <v>791</v>
+        <v>793</v>
       </c>
       <c r="AG186" t="s" s="2">
         <v>76</v>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T10:21:23+00:00</t>
+    <t>2024-10-29T14:54:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-29T14:54:01+00:00</t>
+    <t>2024-10-31T07:20:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-10-31T07:20:54+00:00</t>
+    <t>2024-11-06T10:03:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:03:56+00:00</t>
+    <t>2024-11-06T10:30:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:30:49+00:00</t>
+    <t>2024-11-06T13:09:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T13:09:39+00:00</t>
+    <t>2024-11-06T14:31:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-11T09:21:50+00:00</t>
+    <t>2024-11-11T13:58:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T06:47:57+00:00</t>
+    <t>2024-11-12T08:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T08:54:48+00:00</t>
+    <t>2024-11-12T10:30:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T10:30:22+00:00</t>
+    <t>2024-11-12T12:40:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T12:40:22+00:00</t>
+    <t>2024-11-12T14:33:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:33:00+00:00</t>
+    <t>2024-11-12T14:36:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T14:36:04+00:00</t>
+    <t>2024-11-12T18:20:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:20:22+00:00</t>
+    <t>2024-11-12T18:30:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T18:30:34+00:00</t>
+    <t>2024-11-12T19:00:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:00:23+00:00</t>
+    <t>2024-11-12T19:16:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:16:24+00:00</t>
+    <t>2024-11-12T19:22:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-12T19:22:29+00:00</t>
+    <t>2024-11-14T14:59:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T14:59:39+00:00</t>
+    <t>2024-11-14T15:15:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-14T15:15:53+00:00</t>
+    <t>2024-11-15T07:51:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T07:51:28+00:00</t>
+    <t>2024-11-15T09:58:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T09:58:51+00:00</t>
+    <t>2024-11-15T11:02:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T11:02:30+00:00</t>
+    <t>2024-11-15T19:27:47+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1222,7 +1222,7 @@
     <t>Required to relate the current diagnosis to a package billing code that is then referenced on the individual claim items which are specific to the health condition covered by the package code.</t>
   </si>
   <si>
-    <t>http://tbd.at/MOPED-LKFAbrechnungsGruppe</t>
+    <t>http://example.org/ValueSet/moped-LKFAbrechnungsGruppe-valueset</t>
   </si>
   <si>
     <t>Claim.event</t>
@@ -2809,7 +2809,7 @@
     <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
     <col min="25" max="25" width="124.6484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="52.1640625" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="65.26953125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
     <col min="29" max="29" width="20.59375" customWidth="true" bestFit="true"/>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T19:27:47+00:00</t>
+    <t>2024-11-15T20:19:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-15T20:19:59+00:00</t>
+    <t>2024-11-17T19:53:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T19:53:01+00:00</t>
+    <t>2024-11-17T20:11:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-17T20:11:24+00:00</t>
+    <t>2024-11-20T22:25:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-20T22:25:32+00:00</t>
+    <t>2024-11-22T08:03:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -54,7 +54,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-22T08:03:54+00:00</t>
+    <t>2024-12-12T14:30:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-12-13T08:39:47+00:00</t>
+    <t>2025-01-07T14:12:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:12:01+00:00</t>
+    <t>2025-01-07T14:17:45+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-07T14:17:45+00:00</t>
+    <t>2025-01-14T08:01:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -9,6 +9,9 @@
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Elements" r:id="rId4" sheetId="2"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="true">Elements!$A$1:$AM$186</definedName>
+  </definedNames>
 </workbook>
 </file>
 
@@ -57,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:01:21+00:00</t>
+    <t>2025-01-14T08:16:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2613,6 +2616,21 @@
       <alignment vertical="top" wrapText="true"/>
     </xf>
   </cellXfs>
+  <dxfs count="2">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <bgColor indexed="22"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color indexed="22"/>
+        <i val="true"/>
+      </font>
+    </dxf>
+  </dxfs>
 </styleSheet>
 </file>
 
@@ -2948,7 +2966,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2">
+    <row r="2" hidden="true">
       <c r="A2" t="s" s="2">
         <v>30</v>
       </c>
@@ -3059,7 +3077,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="3">
+    <row r="3" hidden="true">
       <c r="A3" t="s" s="2">
         <v>87</v>
       </c>
@@ -3170,7 +3188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4">
+    <row r="4" hidden="true">
       <c r="A4" t="s" s="2">
         <v>95</v>
       </c>
@@ -3279,7 +3297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5">
+    <row r="5" hidden="true">
       <c r="A5" t="s" s="2">
         <v>101</v>
       </c>
@@ -3390,7 +3408,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6">
+    <row r="6" hidden="true">
       <c r="A6" t="s" s="2">
         <v>107</v>
       </c>
@@ -3501,7 +3519,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7">
+    <row r="7" hidden="true">
       <c r="A7" t="s" s="2">
         <v>116</v>
       </c>
@@ -3612,7 +3630,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="8">
+    <row r="8" hidden="true">
       <c r="A8" t="s" s="2">
         <v>125</v>
       </c>
@@ -3723,7 +3741,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="9">
+    <row r="9" hidden="true">
       <c r="A9" t="s" s="2">
         <v>134</v>
       </c>
@@ -3830,7 +3848,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10">
+    <row r="10" hidden="true">
       <c r="A10" t="s" s="2">
         <v>142</v>
       </c>
@@ -3943,7 +3961,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11">
+    <row r="11" hidden="true">
       <c r="A11" t="s" s="2">
         <v>148</v>
       </c>
@@ -3964,7 +3982,7 @@
         <v>88</v>
       </c>
       <c r="H11" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I11" t="s" s="2">
         <v>20</v>
@@ -4054,7 +4072,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12">
+    <row r="12" hidden="true">
       <c r="A12" t="s" s="2">
         <v>152</v>
       </c>
@@ -4075,7 +4093,7 @@
         <v>78</v>
       </c>
       <c r="H12" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I12" t="s" s="2">
         <v>20</v>
@@ -4165,7 +4183,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13">
+    <row r="13" hidden="true">
       <c r="A13" t="s" s="2">
         <v>157</v>
       </c>
@@ -4276,7 +4294,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14">
+    <row r="14" hidden="true">
       <c r="A14" t="s" s="2">
         <v>162</v>
       </c>
@@ -4297,7 +4315,7 @@
         <v>88</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>20</v>
+        <v>89</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>20</v>
@@ -4387,7 +4405,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15">
+    <row r="15" hidden="true">
       <c r="A15" t="s" s="2">
         <v>167</v>
       </c>
@@ -4498,7 +4516,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16">
+    <row r="16" hidden="true">
       <c r="A16" t="s" s="2">
         <v>172</v>
       </c>
@@ -4609,7 +4627,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17">
+    <row r="17" hidden="true">
       <c r="A17" t="s" s="2">
         <v>177</v>
       </c>
@@ -4722,7 +4740,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="18">
+    <row r="18" hidden="true">
       <c r="A18" t="s" s="2">
         <v>184</v>
       </c>
@@ -4833,7 +4851,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19">
+    <row r="19" hidden="true">
       <c r="A19" t="s" s="2">
         <v>192</v>
       </c>
@@ -4944,7 +4962,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20">
+    <row r="20" hidden="true">
       <c r="A20" t="s" s="2">
         <v>196</v>
       </c>
@@ -5057,7 +5075,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21">
+    <row r="21" hidden="true">
       <c r="A21" t="s" s="2">
         <v>205</v>
       </c>
@@ -5170,7 +5188,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22">
+    <row r="22" hidden="true">
       <c r="A22" t="s" s="2">
         <v>215</v>
       </c>
@@ -5283,7 +5301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23">
+    <row r="23" hidden="true">
       <c r="A23" t="s" s="2">
         <v>223</v>
       </c>
@@ -5394,7 +5412,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24">
+    <row r="24" hidden="true">
       <c r="A24" t="s" s="2">
         <v>229</v>
       </c>
@@ -5505,7 +5523,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25">
+    <row r="25" hidden="true">
       <c r="A25" t="s" s="2">
         <v>236</v>
       </c>
@@ -5618,7 +5636,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26">
+    <row r="26" hidden="true">
       <c r="A26" t="s" s="2">
         <v>243</v>
       </c>
@@ -5731,7 +5749,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27">
+    <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
         <v>251</v>
       </c>
@@ -5842,7 +5860,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28">
+    <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
         <v>257</v>
       </c>
@@ -5951,7 +5969,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29">
+    <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
         <v>262</v>
       </c>
@@ -6062,7 +6080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30">
+    <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
         <v>268</v>
       </c>
@@ -6175,7 +6193,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31">
+    <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
         <v>276</v>
       </c>
@@ -6288,7 +6306,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32">
+    <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
         <v>284</v>
       </c>
@@ -6401,7 +6419,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33">
+    <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
         <v>290</v>
       </c>
@@ -6510,7 +6528,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="34">
+    <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
         <v>297</v>
       </c>
@@ -6621,7 +6639,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="35">
+    <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
         <v>301</v>
       </c>
@@ -6734,7 +6752,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="36">
+    <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
         <v>306</v>
       </c>
@@ -6845,7 +6863,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37">
+    <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
         <v>311</v>
       </c>
@@ -6958,7 +6976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38">
+    <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
         <v>318</v>
       </c>
@@ -7071,7 +7089,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39">
+    <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
         <v>323</v>
       </c>
@@ -7182,7 +7200,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40">
+    <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
         <v>328</v>
       </c>
@@ -7295,7 +7313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="41">
+    <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
         <v>333</v>
       </c>
@@ -7408,7 +7426,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="42">
+    <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
         <v>338</v>
       </c>
@@ -7517,7 +7535,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="43">
+    <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
         <v>339</v>
       </c>
@@ -7628,7 +7646,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="44">
+    <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
         <v>340</v>
       </c>
@@ -7741,7 +7759,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="45">
+    <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
         <v>341</v>
       </c>
@@ -7852,7 +7870,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46">
+    <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
         <v>347</v>
       </c>
@@ -7965,7 +7983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47">
+    <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
         <v>353</v>
       </c>
@@ -8078,7 +8096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48">
+    <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
         <v>360</v>
       </c>
@@ -8189,7 +8207,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49">
+    <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
         <v>368</v>
       </c>
@@ -8304,7 +8322,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50">
+    <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
         <v>372</v>
       </c>
@@ -8419,7 +8437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51">
+    <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
         <v>376</v>
       </c>
@@ -8530,7 +8548,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52">
+    <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
         <v>382</v>
       </c>
@@ -8641,7 +8659,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53">
+    <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
         <v>388</v>
       </c>
@@ -8750,7 +8768,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54">
+    <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
         <v>391</v>
       </c>
@@ -8859,7 +8877,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="55">
+    <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
         <v>392</v>
       </c>
@@ -8970,7 +8988,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="56">
+    <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
         <v>393</v>
       </c>
@@ -9083,7 +9101,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="57">
+    <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
         <v>394</v>
       </c>
@@ -9190,7 +9208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58">
+    <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
         <v>398</v>
       </c>
@@ -9299,7 +9317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59">
+    <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
         <v>402</v>
       </c>
@@ -9410,7 +9428,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60">
+    <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
         <v>406</v>
       </c>
@@ -9519,7 +9537,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="61">
+    <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
         <v>407</v>
       </c>
@@ -9630,7 +9648,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="62">
+    <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
         <v>408</v>
       </c>
@@ -9743,7 +9761,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="63">
+    <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
         <v>409</v>
       </c>
@@ -9854,7 +9872,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="64">
+    <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
         <v>414</v>
       </c>
@@ -9965,7 +9983,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="65">
+    <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
         <v>420</v>
       </c>
@@ -10078,7 +10096,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66">
+    <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
         <v>426</v>
       </c>
@@ -10191,7 +10209,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67">
+    <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
         <v>433</v>
       </c>
@@ -10300,7 +10318,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68">
+    <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
         <v>438</v>
       </c>
@@ -10413,7 +10431,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="69">
+    <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
         <v>445</v>
       </c>
@@ -10522,7 +10540,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="70">
+    <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
         <v>446</v>
       </c>
@@ -10633,7 +10651,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="71">
+    <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
         <v>447</v>
       </c>
@@ -10746,7 +10764,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="72">
+    <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
         <v>448</v>
       </c>
@@ -10857,7 +10875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73">
+    <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
         <v>452</v>
       </c>
@@ -10970,7 +10988,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74">
+    <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
         <v>459</v>
       </c>
@@ -11081,7 +11099,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="75">
+    <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
         <v>465</v>
       </c>
@@ -11190,7 +11208,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76">
+    <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
         <v>469</v>
       </c>
@@ -11303,7 +11321,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="77">
+    <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
         <v>475</v>
       </c>
@@ -11416,7 +11434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78">
+    <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
         <v>482</v>
       </c>
@@ -11527,7 +11545,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79">
+    <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
         <v>487</v>
       </c>
@@ -11636,7 +11654,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="80">
+    <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
         <v>488</v>
       </c>
@@ -11747,7 +11765,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="81">
+    <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
         <v>489</v>
       </c>
@@ -11860,7 +11878,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="82">
+    <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
         <v>490</v>
       </c>
@@ -11973,7 +11991,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83">
+    <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
         <v>495</v>
       </c>
@@ -12084,7 +12102,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84">
+    <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
         <v>502</v>
       </c>
@@ -12197,7 +12215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="85">
+    <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
         <v>509</v>
       </c>
@@ -12308,7 +12326,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="86">
+    <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
         <v>515</v>
       </c>
@@ -12419,7 +12437,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="87">
+    <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
         <v>519</v>
       </c>
@@ -12528,7 +12546,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="88">
+    <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
         <v>520</v>
       </c>
@@ -12635,7 +12653,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="89">
+    <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
         <v>521</v>
       </c>
@@ -12746,7 +12764,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="90">
+    <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
         <v>526</v>
       </c>
@@ -12859,7 +12877,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="91">
+    <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
         <v>527</v>
       </c>
@@ -12970,7 +12988,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="92">
+    <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
         <v>531</v>
       </c>
@@ -13083,7 +13101,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="93">
+    <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
         <v>536</v>
       </c>
@@ -13194,7 +13212,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94">
+    <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
         <v>540</v>
       </c>
@@ -13305,7 +13323,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="95">
+    <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
         <v>547</v>
       </c>
@@ -13416,7 +13434,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96">
+    <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
         <v>552</v>
       </c>
@@ -13529,7 +13547,7 @@
         <v>557</v>
       </c>
     </row>
-    <row r="97">
+    <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
         <v>558</v>
       </c>
@@ -13638,7 +13656,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="98">
+    <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
         <v>559</v>
       </c>
@@ -13749,7 +13767,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="99">
+    <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
         <v>560</v>
       </c>
@@ -13862,7 +13880,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="100">
+    <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
         <v>561</v>
       </c>
@@ -13973,7 +13991,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="101">
+    <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
         <v>565</v>
       </c>
@@ -14086,7 +14104,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="102">
+    <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
         <v>570</v>
       </c>
@@ -14199,7 +14217,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="103">
+    <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
         <v>575</v>
       </c>
@@ -14310,7 +14328,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="104">
+    <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
         <v>580</v>
       </c>
@@ -14421,7 +14439,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105">
+    <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
         <v>584</v>
       </c>
@@ -14534,7 +14552,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="106">
+    <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
         <v>589</v>
       </c>
@@ -14647,7 +14665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="107">
+    <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
         <v>595</v>
       </c>
@@ -14758,7 +14776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="108">
+    <row r="108" hidden="true">
       <c r="A108" t="s" s="2">
         <v>599</v>
       </c>
@@ -14867,7 +14885,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="109">
+    <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
         <v>600</v>
       </c>
@@ -14978,7 +14996,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="110">
+    <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
         <v>601</v>
       </c>
@@ -15091,7 +15109,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="111">
+    <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
         <v>602</v>
       </c>
@@ -15204,7 +15222,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112">
+    <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
         <v>608</v>
       </c>
@@ -15315,7 +15333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="113">
+    <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
         <v>614</v>
       </c>
@@ -15426,7 +15444,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="114">
+    <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
         <v>619</v>
       </c>
@@ -15537,7 +15555,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115">
+    <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
         <v>624</v>
       </c>
@@ -15648,7 +15666,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="116">
+    <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
         <v>628</v>
       </c>
@@ -15757,7 +15775,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="117">
+    <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
         <v>629</v>
       </c>
@@ -15868,7 +15886,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="118">
+    <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
         <v>630</v>
       </c>
@@ -15981,7 +15999,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="119">
+    <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
         <v>631</v>
       </c>
@@ -16092,7 +16110,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="120">
+    <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
         <v>635</v>
       </c>
@@ -16203,7 +16221,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="121">
+    <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
         <v>636</v>
       </c>
@@ -16314,7 +16332,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="122">
+    <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
         <v>640</v>
       </c>
@@ -16425,7 +16443,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="123">
+    <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
         <v>644</v>
       </c>
@@ -16536,7 +16554,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="124">
+    <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
         <v>648</v>
       </c>
@@ -16647,7 +16665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="125">
+    <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
         <v>652</v>
       </c>
@@ -16758,7 +16776,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="126">
+    <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
         <v>658</v>
       </c>
@@ -16871,7 +16889,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127">
+    <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
         <v>665</v>
       </c>
@@ -16984,7 +17002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="128">
+    <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
         <v>673</v>
       </c>
@@ -17091,7 +17109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="129">
+    <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
         <v>677</v>
       </c>
@@ -17202,7 +17220,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="130">
+    <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
         <v>682</v>
       </c>
@@ -17315,7 +17333,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="131">
+    <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
         <v>689</v>
       </c>
@@ -17428,7 +17446,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="132">
+    <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
         <v>696</v>
       </c>
@@ -17539,7 +17557,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="133">
+    <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
         <v>700</v>
       </c>
@@ -17650,7 +17668,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="134">
+    <row r="134" hidden="true">
       <c r="A134" t="s" s="2">
         <v>707</v>
       </c>
@@ -17761,7 +17779,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="135">
+    <row r="135" hidden="true">
       <c r="A135" t="s" s="2">
         <v>708</v>
       </c>
@@ -17872,7 +17890,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="136">
+    <row r="136" hidden="true">
       <c r="A136" t="s" s="2">
         <v>713</v>
       </c>
@@ -17983,7 +18001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137">
+    <row r="137" hidden="true">
       <c r="A137" t="s" s="2">
         <v>717</v>
       </c>
@@ -18096,7 +18114,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138">
+    <row r="138" hidden="true">
       <c r="A138" t="s" s="2">
         <v>723</v>
       </c>
@@ -18207,7 +18225,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="139">
+    <row r="139" hidden="true">
       <c r="A139" t="s" s="2">
         <v>727</v>
       </c>
@@ -18320,7 +18338,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="140">
+    <row r="140" hidden="true">
       <c r="A140" t="s" s="2">
         <v>732</v>
       </c>
@@ -18431,7 +18449,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="141">
+    <row r="141" hidden="true">
       <c r="A141" t="s" s="2">
         <v>733</v>
       </c>
@@ -18540,7 +18558,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="142">
+    <row r="142" hidden="true">
       <c r="A142" t="s" s="2">
         <v>736</v>
       </c>
@@ -18649,7 +18667,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="143">
+    <row r="143" hidden="true">
       <c r="A143" t="s" s="2">
         <v>737</v>
       </c>
@@ -18760,7 +18778,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="144">
+    <row r="144" hidden="true">
       <c r="A144" t="s" s="2">
         <v>738</v>
       </c>
@@ -18873,7 +18891,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="145">
+    <row r="145" hidden="true">
       <c r="A145" t="s" s="2">
         <v>739</v>
       </c>
@@ -18984,7 +19002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="146">
+    <row r="146" hidden="true">
       <c r="A146" t="s" s="2">
         <v>746</v>
       </c>
@@ -19093,7 +19111,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="147">
+    <row r="147" hidden="true">
       <c r="A147" t="s" s="2">
         <v>750</v>
       </c>
@@ -19206,7 +19224,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="148">
+    <row r="148" hidden="true">
       <c r="A148" t="s" s="2">
         <v>752</v>
       </c>
@@ -19317,7 +19335,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="149">
+    <row r="149" hidden="true">
       <c r="A149" t="s" s="2">
         <v>754</v>
       </c>
@@ -19426,7 +19444,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="150">
+    <row r="150" hidden="true">
       <c r="A150" t="s" s="2">
         <v>755</v>
       </c>
@@ -19537,7 +19555,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="151">
+    <row r="151" hidden="true">
       <c r="A151" t="s" s="2">
         <v>756</v>
       </c>
@@ -19650,7 +19668,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="152">
+    <row r="152" hidden="true">
       <c r="A152" t="s" s="2">
         <v>757</v>
       </c>
@@ -19761,7 +19779,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="153">
+    <row r="153" hidden="true">
       <c r="A153" t="s" s="2">
         <v>758</v>
       </c>
@@ -19872,7 +19890,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="154">
+    <row r="154" hidden="true">
       <c r="A154" t="s" s="2">
         <v>759</v>
       </c>
@@ -19983,7 +20001,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="155">
+    <row r="155" hidden="true">
       <c r="A155" t="s" s="2">
         <v>760</v>
       </c>
@@ -20096,7 +20114,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="156">
+    <row r="156" hidden="true">
       <c r="A156" t="s" s="2">
         <v>761</v>
       </c>
@@ -20209,7 +20227,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="157">
+    <row r="157" hidden="true">
       <c r="A157" t="s" s="2">
         <v>762</v>
       </c>
@@ -20316,7 +20334,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="158">
+    <row r="158" hidden="true">
       <c r="A158" t="s" s="2">
         <v>763</v>
       </c>
@@ -20429,7 +20447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="159">
+    <row r="159" hidden="true">
       <c r="A159" t="s" s="2">
         <v>766</v>
       </c>
@@ -20542,7 +20560,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="160">
+    <row r="160" hidden="true">
       <c r="A160" t="s" s="2">
         <v>767</v>
       </c>
@@ -20653,7 +20671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="161">
+    <row r="161" hidden="true">
       <c r="A161" t="s" s="2">
         <v>768</v>
       </c>
@@ -20764,7 +20782,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="162">
+    <row r="162" hidden="true">
       <c r="A162" t="s" s="2">
         <v>769</v>
       </c>
@@ -20875,7 +20893,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="163">
+    <row r="163" hidden="true">
       <c r="A163" t="s" s="2">
         <v>770</v>
       </c>
@@ -20988,7 +21006,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="164">
+    <row r="164" hidden="true">
       <c r="A164" t="s" s="2">
         <v>771</v>
       </c>
@@ -21099,7 +21117,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="165">
+    <row r="165" hidden="true">
       <c r="A165" t="s" s="2">
         <v>772</v>
       </c>
@@ -21212,7 +21230,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="166">
+    <row r="166" hidden="true">
       <c r="A166" t="s" s="2">
         <v>774</v>
       </c>
@@ -21323,7 +21341,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="167">
+    <row r="167" hidden="true">
       <c r="A167" t="s" s="2">
         <v>775</v>
       </c>
@@ -21434,7 +21452,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="168">
+    <row r="168" hidden="true">
       <c r="A168" t="s" s="2">
         <v>776</v>
       </c>
@@ -21543,7 +21561,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="169">
+    <row r="169" hidden="true">
       <c r="A169" t="s" s="2">
         <v>777</v>
       </c>
@@ -21654,7 +21672,7 @@
         <v>296</v>
       </c>
     </row>
-    <row r="170">
+    <row r="170" hidden="true">
       <c r="A170" t="s" s="2">
         <v>778</v>
       </c>
@@ -21767,7 +21785,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="171">
+    <row r="171" hidden="true">
       <c r="A171" t="s" s="2">
         <v>779</v>
       </c>
@@ -21878,7 +21896,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="172">
+    <row r="172" hidden="true">
       <c r="A172" t="s" s="2">
         <v>780</v>
       </c>
@@ -21989,7 +22007,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="173">
+    <row r="173" hidden="true">
       <c r="A173" t="s" s="2">
         <v>781</v>
       </c>
@@ -22100,7 +22118,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="174">
+    <row r="174" hidden="true">
       <c r="A174" t="s" s="2">
         <v>782</v>
       </c>
@@ -22213,7 +22231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="175">
+    <row r="175" hidden="true">
       <c r="A175" t="s" s="2">
         <v>783</v>
       </c>
@@ -22326,7 +22344,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="176">
+    <row r="176" hidden="true">
       <c r="A176" t="s" s="2">
         <v>784</v>
       </c>
@@ -22433,7 +22451,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="177">
+    <row r="177" hidden="true">
       <c r="A177" t="s" s="2">
         <v>785</v>
       </c>
@@ -22546,7 +22564,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="178">
+    <row r="178" hidden="true">
       <c r="A178" t="s" s="2">
         <v>786</v>
       </c>
@@ -22659,7 +22677,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="179">
+    <row r="179" hidden="true">
       <c r="A179" t="s" s="2">
         <v>787</v>
       </c>
@@ -22770,7 +22788,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="180">
+    <row r="180" hidden="true">
       <c r="A180" t="s" s="2">
         <v>788</v>
       </c>
@@ -22881,7 +22899,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="181">
+    <row r="181" hidden="true">
       <c r="A181" t="s" s="2">
         <v>789</v>
       </c>
@@ -22992,7 +23010,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="182">
+    <row r="182" hidden="true">
       <c r="A182" t="s" s="2">
         <v>790</v>
       </c>
@@ -23105,7 +23123,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="183">
+    <row r="183" hidden="true">
       <c r="A183" t="s" s="2">
         <v>791</v>
       </c>
@@ -23216,7 +23234,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="184">
+    <row r="184" hidden="true">
       <c r="A184" t="s" s="2">
         <v>792</v>
       </c>
@@ -23329,7 +23347,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="185">
+    <row r="185" hidden="true">
       <c r="A185" t="s" s="2">
         <v>794</v>
       </c>
@@ -23440,7 +23458,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="186">
+    <row r="186" hidden="true">
       <c r="A186" t="s" s="2">
         <v>795</v>
       </c>
@@ -23552,6 +23570,24 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:AM186">
+    <filterColumn colId="6">
+      <customFilters>
+        <customFilter operator="notEqual" val=" "/>
+      </customFilters>
+    </filterColumn>
+    <filterColumn colId="26">
+      <filters blank="true"/>
+    </filterColumn>
+  </autoFilter>
+  <conditionalFormatting sqref="A2:AI185">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>$G2&lt;&gt;"Y"</formula>
+    </cfRule>
+    <cfRule type="expression" dxfId="1" priority="2">
+      <formula>$Q2&lt;&gt;""</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
 </file>
--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-01-14T08:16:01+00:00</t>
+    <t>2025-02-07T07:07:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T07:07:15+00:00</t>
+    <t>2025-02-07T10:07:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-07T10:07:52+00:00</t>
+    <t>2025-02-10T08:30:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:30:06+00:00</t>
+    <t>2025-02-10T08:38:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-10T08:38:31+00:00</t>
+    <t>2025-02-11T11:17:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
+++ b/r5-ELGA-MOPED-main/StructureDefinition-MOPEDClaim.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-02-11T11:17:52+00:00</t>
+    <t>2025-02-11T16:50:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
